--- a/apps/nuxt/i18n/i18n.xlsx
+++ b/apps/nuxt/i18n/i18n.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12200"/>
+    <workbookView windowWidth="30720" windowHeight="13500"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7890" uniqueCount="7168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7890" uniqueCount="7156">
   <si>
     <t>key</t>
   </si>
@@ -19720,46 +19720,10 @@
     <t>Важливе повідомлення</t>
   </si>
   <si>
-    <t>dont_remind</t>
-  </si>
-  <si>
-    <t>不再提醒</t>
-  </si>
-  <si>
-    <t>Don't remind again</t>
-  </si>
-  <si>
-    <t>再度通知しない</t>
-  </si>
-  <si>
-    <t>다시 알리지 않음</t>
-  </si>
-  <si>
-    <t>No recordar de nuevo</t>
-  </si>
-  <si>
-    <t>Não lembrar novamente</t>
-  </si>
-  <si>
-    <t>Nicht mehr erinnern</t>
-  </si>
-  <si>
-    <t>Ne plus rappeler</t>
-  </si>
-  <si>
-    <t>Больше не напоминать</t>
-  </si>
-  <si>
-    <t>ไม่ต้องเตือนอีก</t>
-  </si>
-  <si>
-    <t>Không nhắc lại</t>
-  </si>
-  <si>
-    <t>Jangan Ingatkan Lagi</t>
-  </si>
-  <si>
-    <t>Більше не нагадувати</t>
+    <t>dont_show</t>
+  </si>
+  <si>
+    <t>不再显示</t>
   </si>
   <si>
     <t>function_desc</t>
@@ -22565,7 +22529,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:O526"/>
-  <sheetFormatPr defaultColWidth="9.625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.625" defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="47" customWidth="1"/>
     <col min="2" max="2" width="21.875" customWidth="1"/>
@@ -44528,40 +44492,40 @@
         <v>6560</v>
       </c>
       <c r="C468" t="s">
-        <v>6561</v>
+        <v>6560</v>
       </c>
       <c r="D468" t="s">
-        <v>6562</v>
+        <v>6560</v>
       </c>
       <c r="E468" t="s">
-        <v>6563</v>
+        <v>6560</v>
       </c>
       <c r="F468" t="s">
-        <v>6564</v>
+        <v>6560</v>
       </c>
       <c r="G468" t="s">
-        <v>6565</v>
+        <v>6560</v>
       </c>
       <c r="H468" t="s">
-        <v>6566</v>
+        <v>6560</v>
       </c>
       <c r="I468" t="s">
-        <v>6567</v>
+        <v>6560</v>
       </c>
       <c r="J468" t="s">
-        <v>6568</v>
+        <v>6560</v>
       </c>
       <c r="K468" t="s">
-        <v>6569</v>
+        <v>6560</v>
       </c>
       <c r="L468" t="s">
-        <v>6570</v>
+        <v>6560</v>
       </c>
       <c r="M468" t="s">
-        <v>6571</v>
+        <v>6560</v>
       </c>
       <c r="N468" t="s">
-        <v>6572</v>
+        <v>6560</v>
       </c>
       <c r="O468" t="s">
         <v>6560</v>
@@ -44569,54 +44533,54 @@
     </row>
     <row r="469" spans="1:15">
       <c r="A469" t="s">
-        <v>6573</v>
+        <v>6561</v>
       </c>
       <c r="B469" t="s">
-        <v>6574</v>
+        <v>6562</v>
       </c>
       <c r="C469" t="s">
-        <v>6575</v>
+        <v>6563</v>
       </c>
       <c r="D469" t="s">
-        <v>6576</v>
+        <v>6564</v>
       </c>
       <c r="E469" t="s">
-        <v>6577</v>
+        <v>6565</v>
       </c>
       <c r="F469" t="s">
-        <v>6578</v>
+        <v>6566</v>
       </c>
       <c r="G469" t="s">
         <v>724</v>
       </c>
       <c r="H469" t="s">
-        <v>6579</v>
+        <v>6567</v>
       </c>
       <c r="I469" t="s">
-        <v>6580</v>
+        <v>6568</v>
       </c>
       <c r="J469" t="s">
-        <v>6581</v>
+        <v>6569</v>
       </c>
       <c r="K469" t="s">
-        <v>6582</v>
+        <v>6570</v>
       </c>
       <c r="L469" t="s">
-        <v>6583</v>
+        <v>6571</v>
       </c>
       <c r="M469" t="s">
-        <v>6584</v>
+        <v>6572</v>
       </c>
       <c r="N469" t="s">
-        <v>6585</v>
+        <v>6573</v>
       </c>
       <c r="O469" t="s">
-        <v>6574</v>
+        <v>6562</v>
       </c>
     </row>
     <row r="470" spans="1:15">
       <c r="A470" t="s">
-        <v>6586</v>
+        <v>6574</v>
       </c>
       <c r="B470" t="s">
         <v>2368</v>
@@ -44631,7 +44595,7 @@
         <v>2371</v>
       </c>
       <c r="F470" t="s">
-        <v>6587</v>
+        <v>6575</v>
       </c>
       <c r="G470" t="s">
         <v>2373</v>
@@ -44640,136 +44604,136 @@
         <v>2374</v>
       </c>
       <c r="I470" t="s">
-        <v>6588</v>
+        <v>6576</v>
       </c>
       <c r="J470" t="s">
         <v>2376</v>
       </c>
       <c r="K470" t="s">
-        <v>6589</v>
+        <v>6577</v>
       </c>
       <c r="L470" t="s">
         <v>2378</v>
       </c>
       <c r="M470" t="s">
-        <v>6590</v>
+        <v>6578</v>
       </c>
       <c r="N470" t="s">
         <v>2380</v>
       </c>
       <c r="O470" t="s">
-        <v>6591</v>
+        <v>6579</v>
       </c>
     </row>
     <row r="471" spans="1:15">
       <c r="A471" t="s">
+        <v>6580</v>
+      </c>
+      <c r="B471" t="s">
+        <v>6581</v>
+      </c>
+      <c r="C471" t="s">
+        <v>6582</v>
+      </c>
+      <c r="D471" t="s">
+        <v>6583</v>
+      </c>
+      <c r="E471" t="s">
+        <v>6584</v>
+      </c>
+      <c r="F471" t="s">
+        <v>6585</v>
+      </c>
+      <c r="G471" t="s">
+        <v>6586</v>
+      </c>
+      <c r="H471" t="s">
+        <v>6587</v>
+      </c>
+      <c r="I471" t="s">
+        <v>6588</v>
+      </c>
+      <c r="J471" t="s">
+        <v>6589</v>
+      </c>
+      <c r="K471" t="s">
+        <v>6590</v>
+      </c>
+      <c r="L471" t="s">
+        <v>6591</v>
+      </c>
+      <c r="M471" t="s">
         <v>6592</v>
       </c>
-      <c r="B471" t="s">
+      <c r="N471" t="s">
         <v>6593</v>
       </c>
-      <c r="C471" t="s">
+      <c r="O471" t="s">
         <v>6594</v>
-      </c>
-      <c r="D471" t="s">
-        <v>6595</v>
-      </c>
-      <c r="E471" t="s">
-        <v>6596</v>
-      </c>
-      <c r="F471" t="s">
-        <v>6597</v>
-      </c>
-      <c r="G471" t="s">
-        <v>6598</v>
-      </c>
-      <c r="H471" t="s">
-        <v>6599</v>
-      </c>
-      <c r="I471" t="s">
-        <v>6600</v>
-      </c>
-      <c r="J471" t="s">
-        <v>6601</v>
-      </c>
-      <c r="K471" t="s">
-        <v>6602</v>
-      </c>
-      <c r="L471" t="s">
-        <v>6603</v>
-      </c>
-      <c r="M471" t="s">
-        <v>6604</v>
-      </c>
-      <c r="N471" t="s">
-        <v>6605</v>
-      </c>
-      <c r="O471" t="s">
-        <v>6606</v>
       </c>
     </row>
     <row r="472" spans="1:15">
       <c r="A472" t="s">
+        <v>6595</v>
+      </c>
+      <c r="B472" t="s">
+        <v>6596</v>
+      </c>
+      <c r="C472" t="s">
+        <v>6597</v>
+      </c>
+      <c r="D472" t="s">
+        <v>6598</v>
+      </c>
+      <c r="E472" t="s">
+        <v>6599</v>
+      </c>
+      <c r="F472" t="s">
+        <v>6600</v>
+      </c>
+      <c r="G472" t="s">
+        <v>6601</v>
+      </c>
+      <c r="H472" t="s">
+        <v>6602</v>
+      </c>
+      <c r="I472" t="s">
+        <v>6603</v>
+      </c>
+      <c r="J472" t="s">
+        <v>6604</v>
+      </c>
+      <c r="K472" t="s">
+        <v>6605</v>
+      </c>
+      <c r="L472" t="s">
+        <v>6606</v>
+      </c>
+      <c r="M472" t="s">
         <v>6607</v>
       </c>
-      <c r="B472" t="s">
+      <c r="N472" t="s">
         <v>6608</v>
       </c>
-      <c r="C472" t="s">
+      <c r="O472" t="s">
         <v>6609</v>
-      </c>
-      <c r="D472" t="s">
-        <v>6610</v>
-      </c>
-      <c r="E472" t="s">
-        <v>6611</v>
-      </c>
-      <c r="F472" t="s">
-        <v>6612</v>
-      </c>
-      <c r="G472" t="s">
-        <v>6613</v>
-      </c>
-      <c r="H472" t="s">
-        <v>6614</v>
-      </c>
-      <c r="I472" t="s">
-        <v>6615</v>
-      </c>
-      <c r="J472" t="s">
-        <v>6616</v>
-      </c>
-      <c r="K472" t="s">
-        <v>6617</v>
-      </c>
-      <c r="L472" t="s">
-        <v>6618</v>
-      </c>
-      <c r="M472" t="s">
-        <v>6619</v>
-      </c>
-      <c r="N472" t="s">
-        <v>6620</v>
-      </c>
-      <c r="O472" t="s">
-        <v>6621</v>
       </c>
     </row>
     <row r="473" spans="1:15">
       <c r="A473" t="s">
-        <v>6622</v>
+        <v>6610</v>
       </c>
       <c r="B473" t="s">
         <v>2383</v>
       </c>
       <c r="C473" t="s">
-        <v>6623</v>
+        <v>6611</v>
       </c>
       <c r="D473" t="s">
         <v>2385</v>
       </c>
       <c r="E473" t="s">
-        <v>6624</v>
+        <v>6612</v>
       </c>
       <c r="F473" t="s">
         <v>2387</v>
@@ -44781,2516 +44745,2516 @@
         <v>2389</v>
       </c>
       <c r="I473" t="s">
-        <v>6625</v>
+        <v>6613</v>
       </c>
       <c r="J473" t="s">
-        <v>6626</v>
+        <v>6614</v>
       </c>
       <c r="K473" t="s">
-        <v>6627</v>
+        <v>6615</v>
       </c>
       <c r="L473" t="s">
-        <v>6628</v>
+        <v>6616</v>
       </c>
       <c r="M473" t="s">
-        <v>6629</v>
+        <v>6617</v>
       </c>
       <c r="N473" t="s">
-        <v>6630</v>
+        <v>6618</v>
       </c>
       <c r="O473" t="s">
-        <v>6631</v>
+        <v>6619</v>
       </c>
     </row>
     <row r="474" spans="1:15">
       <c r="A474" t="s">
-        <v>6632</v>
+        <v>6620</v>
       </c>
       <c r="B474" t="s">
         <v>2398</v>
       </c>
       <c r="C474" t="s">
+        <v>6621</v>
+      </c>
+      <c r="D474" t="s">
+        <v>6622</v>
+      </c>
+      <c r="E474" t="s">
+        <v>6623</v>
+      </c>
+      <c r="F474" t="s">
+        <v>6624</v>
+      </c>
+      <c r="G474" t="s">
+        <v>6625</v>
+      </c>
+      <c r="H474" t="s">
+        <v>6626</v>
+      </c>
+      <c r="I474" t="s">
+        <v>6627</v>
+      </c>
+      <c r="J474" t="s">
+        <v>6628</v>
+      </c>
+      <c r="K474" t="s">
+        <v>6629</v>
+      </c>
+      <c r="L474" t="s">
+        <v>6630</v>
+      </c>
+      <c r="M474" t="s">
+        <v>6631</v>
+      </c>
+      <c r="N474" t="s">
+        <v>6632</v>
+      </c>
+      <c r="O474" t="s">
         <v>6633</v>
-      </c>
-      <c r="D474" t="s">
-        <v>6634</v>
-      </c>
-      <c r="E474" t="s">
-        <v>6635</v>
-      </c>
-      <c r="F474" t="s">
-        <v>6636</v>
-      </c>
-      <c r="G474" t="s">
-        <v>6637</v>
-      </c>
-      <c r="H474" t="s">
-        <v>6638</v>
-      </c>
-      <c r="I474" t="s">
-        <v>6639</v>
-      </c>
-      <c r="J474" t="s">
-        <v>6640</v>
-      </c>
-      <c r="K474" t="s">
-        <v>6641</v>
-      </c>
-      <c r="L474" t="s">
-        <v>6642</v>
-      </c>
-      <c r="M474" t="s">
-        <v>6643</v>
-      </c>
-      <c r="N474" t="s">
-        <v>6644</v>
-      </c>
-      <c r="O474" t="s">
-        <v>6645</v>
       </c>
     </row>
     <row r="475" spans="1:15">
       <c r="A475" t="s">
+        <v>6634</v>
+      </c>
+      <c r="B475" t="s">
+        <v>6635</v>
+      </c>
+      <c r="C475" t="s">
+        <v>6636</v>
+      </c>
+      <c r="D475" t="s">
+        <v>6637</v>
+      </c>
+      <c r="E475" t="s">
+        <v>6638</v>
+      </c>
+      <c r="F475" t="s">
+        <v>6639</v>
+      </c>
+      <c r="G475" t="s">
+        <v>6640</v>
+      </c>
+      <c r="H475" t="s">
+        <v>6641</v>
+      </c>
+      <c r="I475" t="s">
+        <v>6642</v>
+      </c>
+      <c r="J475" t="s">
+        <v>6643</v>
+      </c>
+      <c r="K475" t="s">
+        <v>6644</v>
+      </c>
+      <c r="L475" t="s">
+        <v>6645</v>
+      </c>
+      <c r="M475" t="s">
         <v>6646</v>
       </c>
-      <c r="B475" t="s">
+      <c r="N475" t="s">
         <v>6647</v>
       </c>
-      <c r="C475" t="s">
+      <c r="O475" t="s">
         <v>6648</v>
-      </c>
-      <c r="D475" t="s">
-        <v>6649</v>
-      </c>
-      <c r="E475" t="s">
-        <v>6650</v>
-      </c>
-      <c r="F475" t="s">
-        <v>6651</v>
-      </c>
-      <c r="G475" t="s">
-        <v>6652</v>
-      </c>
-      <c r="H475" t="s">
-        <v>6653</v>
-      </c>
-      <c r="I475" t="s">
-        <v>6654</v>
-      </c>
-      <c r="J475" t="s">
-        <v>6655</v>
-      </c>
-      <c r="K475" t="s">
-        <v>6656</v>
-      </c>
-      <c r="L475" t="s">
-        <v>6657</v>
-      </c>
-      <c r="M475" t="s">
-        <v>6658</v>
-      </c>
-      <c r="N475" t="s">
-        <v>6659</v>
-      </c>
-      <c r="O475" t="s">
-        <v>6660</v>
       </c>
     </row>
     <row r="476" spans="1:15">
       <c r="A476" t="s">
+        <v>6649</v>
+      </c>
+      <c r="B476" t="s">
+        <v>6650</v>
+      </c>
+      <c r="C476" t="s">
+        <v>6651</v>
+      </c>
+      <c r="D476" t="s">
+        <v>6652</v>
+      </c>
+      <c r="E476" t="s">
+        <v>6653</v>
+      </c>
+      <c r="F476" t="s">
+        <v>6654</v>
+      </c>
+      <c r="G476" t="s">
+        <v>6655</v>
+      </c>
+      <c r="H476" t="s">
+        <v>6656</v>
+      </c>
+      <c r="I476" t="s">
+        <v>6657</v>
+      </c>
+      <c r="J476" t="s">
+        <v>6658</v>
+      </c>
+      <c r="K476" t="s">
+        <v>6659</v>
+      </c>
+      <c r="L476" t="s">
+        <v>6660</v>
+      </c>
+      <c r="M476" t="s">
         <v>6661</v>
       </c>
-      <c r="B476" t="s">
+      <c r="N476" t="s">
         <v>6662</v>
       </c>
-      <c r="C476" t="s">
+      <c r="O476" t="s">
         <v>6663</v>
-      </c>
-      <c r="D476" t="s">
-        <v>6664</v>
-      </c>
-      <c r="E476" t="s">
-        <v>6665</v>
-      </c>
-      <c r="F476" t="s">
-        <v>6666</v>
-      </c>
-      <c r="G476" t="s">
-        <v>6667</v>
-      </c>
-      <c r="H476" t="s">
-        <v>6668</v>
-      </c>
-      <c r="I476" t="s">
-        <v>6669</v>
-      </c>
-      <c r="J476" t="s">
-        <v>6670</v>
-      </c>
-      <c r="K476" t="s">
-        <v>6671</v>
-      </c>
-      <c r="L476" t="s">
-        <v>6672</v>
-      </c>
-      <c r="M476" t="s">
-        <v>6673</v>
-      </c>
-      <c r="N476" t="s">
-        <v>6674</v>
-      </c>
-      <c r="O476" t="s">
-        <v>6675</v>
       </c>
     </row>
     <row r="477" spans="1:15">
       <c r="A477" t="s">
+        <v>6664</v>
+      </c>
+      <c r="B477" t="s">
+        <v>6665</v>
+      </c>
+      <c r="C477" t="s">
+        <v>6666</v>
+      </c>
+      <c r="D477" t="s">
+        <v>6667</v>
+      </c>
+      <c r="E477" t="s">
+        <v>6668</v>
+      </c>
+      <c r="F477" t="s">
+        <v>6669</v>
+      </c>
+      <c r="G477" t="s">
+        <v>6670</v>
+      </c>
+      <c r="H477" t="s">
+        <v>6671</v>
+      </c>
+      <c r="I477" t="s">
+        <v>6672</v>
+      </c>
+      <c r="J477" t="s">
+        <v>6673</v>
+      </c>
+      <c r="K477" t="s">
+        <v>6674</v>
+      </c>
+      <c r="L477" t="s">
+        <v>6675</v>
+      </c>
+      <c r="M477" t="s">
         <v>6676</v>
       </c>
-      <c r="B477" t="s">
+      <c r="N477" t="s">
         <v>6677</v>
       </c>
-      <c r="C477" t="s">
+      <c r="O477" t="s">
         <v>6678</v>
-      </c>
-      <c r="D477" t="s">
-        <v>6679</v>
-      </c>
-      <c r="E477" t="s">
-        <v>6680</v>
-      </c>
-      <c r="F477" t="s">
-        <v>6681</v>
-      </c>
-      <c r="G477" t="s">
-        <v>6682</v>
-      </c>
-      <c r="H477" t="s">
-        <v>6683</v>
-      </c>
-      <c r="I477" t="s">
-        <v>6684</v>
-      </c>
-      <c r="J477" t="s">
-        <v>6685</v>
-      </c>
-      <c r="K477" t="s">
-        <v>6686</v>
-      </c>
-      <c r="L477" t="s">
-        <v>6687</v>
-      </c>
-      <c r="M477" t="s">
-        <v>6688</v>
-      </c>
-      <c r="N477" t="s">
-        <v>6689</v>
-      </c>
-      <c r="O477" t="s">
-        <v>6690</v>
       </c>
     </row>
     <row r="478" spans="1:15">
       <c r="A478" t="s">
+        <v>6679</v>
+      </c>
+      <c r="B478" t="s">
+        <v>6680</v>
+      </c>
+      <c r="C478" t="s">
+        <v>6681</v>
+      </c>
+      <c r="D478" t="s">
+        <v>6682</v>
+      </c>
+      <c r="E478" t="s">
+        <v>6683</v>
+      </c>
+      <c r="F478" t="s">
+        <v>6684</v>
+      </c>
+      <c r="G478" t="s">
+        <v>6685</v>
+      </c>
+      <c r="H478" t="s">
+        <v>6686</v>
+      </c>
+      <c r="I478" t="s">
+        <v>6687</v>
+      </c>
+      <c r="J478" t="s">
+        <v>6688</v>
+      </c>
+      <c r="K478" t="s">
+        <v>6689</v>
+      </c>
+      <c r="L478" t="s">
+        <v>6690</v>
+      </c>
+      <c r="M478" t="s">
         <v>6691</v>
       </c>
-      <c r="B478" t="s">
+      <c r="N478" t="s">
         <v>6692</v>
       </c>
-      <c r="C478" t="s">
+      <c r="O478" t="s">
         <v>6693</v>
-      </c>
-      <c r="D478" t="s">
-        <v>6694</v>
-      </c>
-      <c r="E478" t="s">
-        <v>6695</v>
-      </c>
-      <c r="F478" t="s">
-        <v>6696</v>
-      </c>
-      <c r="G478" t="s">
-        <v>6697</v>
-      </c>
-      <c r="H478" t="s">
-        <v>6698</v>
-      </c>
-      <c r="I478" t="s">
-        <v>6699</v>
-      </c>
-      <c r="J478" t="s">
-        <v>6700</v>
-      </c>
-      <c r="K478" t="s">
-        <v>6701</v>
-      </c>
-      <c r="L478" t="s">
-        <v>6702</v>
-      </c>
-      <c r="M478" t="s">
-        <v>6703</v>
-      </c>
-      <c r="N478" t="s">
-        <v>6704</v>
-      </c>
-      <c r="O478" t="s">
-        <v>6705</v>
       </c>
     </row>
     <row r="479" spans="1:15">
       <c r="A479" t="s">
+        <v>6694</v>
+      </c>
+      <c r="B479" t="s">
+        <v>6695</v>
+      </c>
+      <c r="C479" t="s">
+        <v>6696</v>
+      </c>
+      <c r="D479" t="s">
+        <v>6697</v>
+      </c>
+      <c r="E479" t="s">
+        <v>6698</v>
+      </c>
+      <c r="F479" t="s">
+        <v>6699</v>
+      </c>
+      <c r="G479" t="s">
+        <v>6700</v>
+      </c>
+      <c r="H479" t="s">
+        <v>6701</v>
+      </c>
+      <c r="I479" t="s">
+        <v>6702</v>
+      </c>
+      <c r="J479" t="s">
+        <v>6703</v>
+      </c>
+      <c r="K479" t="s">
+        <v>6704</v>
+      </c>
+      <c r="L479" t="s">
+        <v>6705</v>
+      </c>
+      <c r="M479" t="s">
         <v>6706</v>
       </c>
-      <c r="B479" t="s">
+      <c r="N479" t="s">
         <v>6707</v>
       </c>
-      <c r="C479" t="s">
+      <c r="O479" t="s">
         <v>6708</v>
-      </c>
-      <c r="D479" t="s">
-        <v>6709</v>
-      </c>
-      <c r="E479" t="s">
-        <v>6710</v>
-      </c>
-      <c r="F479" t="s">
-        <v>6711</v>
-      </c>
-      <c r="G479" t="s">
-        <v>6712</v>
-      </c>
-      <c r="H479" t="s">
-        <v>6713</v>
-      </c>
-      <c r="I479" t="s">
-        <v>6714</v>
-      </c>
-      <c r="J479" t="s">
-        <v>6715</v>
-      </c>
-      <c r="K479" t="s">
-        <v>6716</v>
-      </c>
-      <c r="L479" t="s">
-        <v>6717</v>
-      </c>
-      <c r="M479" t="s">
-        <v>6718</v>
-      </c>
-      <c r="N479" t="s">
-        <v>6719</v>
-      </c>
-      <c r="O479" t="s">
-        <v>6720</v>
       </c>
     </row>
     <row r="480" spans="1:15">
       <c r="A480" t="s">
+        <v>6709</v>
+      </c>
+      <c r="B480" t="s">
+        <v>6710</v>
+      </c>
+      <c r="C480" t="s">
+        <v>6711</v>
+      </c>
+      <c r="D480" t="s">
+        <v>6712</v>
+      </c>
+      <c r="E480" t="s">
+        <v>6713</v>
+      </c>
+      <c r="F480" t="s">
+        <v>6714</v>
+      </c>
+      <c r="G480" t="s">
+        <v>6715</v>
+      </c>
+      <c r="H480" t="s">
+        <v>6716</v>
+      </c>
+      <c r="I480" t="s">
+        <v>6717</v>
+      </c>
+      <c r="J480" t="s">
+        <v>6718</v>
+      </c>
+      <c r="K480" t="s">
+        <v>6719</v>
+      </c>
+      <c r="L480" t="s">
+        <v>6720</v>
+      </c>
+      <c r="M480" t="s">
         <v>6721</v>
       </c>
-      <c r="B480" t="s">
+      <c r="N480" t="s">
         <v>6722</v>
       </c>
-      <c r="C480" t="s">
+      <c r="O480" t="s">
         <v>6723</v>
-      </c>
-      <c r="D480" t="s">
-        <v>6724</v>
-      </c>
-      <c r="E480" t="s">
-        <v>6725</v>
-      </c>
-      <c r="F480" t="s">
-        <v>6726</v>
-      </c>
-      <c r="G480" t="s">
-        <v>6727</v>
-      </c>
-      <c r="H480" t="s">
-        <v>6728</v>
-      </c>
-      <c r="I480" t="s">
-        <v>6729</v>
-      </c>
-      <c r="J480" t="s">
-        <v>6730</v>
-      </c>
-      <c r="K480" t="s">
-        <v>6731</v>
-      </c>
-      <c r="L480" t="s">
-        <v>6732</v>
-      </c>
-      <c r="M480" t="s">
-        <v>6733</v>
-      </c>
-      <c r="N480" t="s">
-        <v>6734</v>
-      </c>
-      <c r="O480" t="s">
-        <v>6735</v>
       </c>
     </row>
     <row r="481" spans="1:15">
       <c r="A481" t="s">
+        <v>6724</v>
+      </c>
+      <c r="B481" t="s">
+        <v>6725</v>
+      </c>
+      <c r="C481" t="s">
+        <v>6726</v>
+      </c>
+      <c r="D481" t="s">
+        <v>6727</v>
+      </c>
+      <c r="E481" t="s">
+        <v>6728</v>
+      </c>
+      <c r="F481" t="s">
+        <v>6729</v>
+      </c>
+      <c r="G481" t="s">
+        <v>6730</v>
+      </c>
+      <c r="H481" t="s">
+        <v>6731</v>
+      </c>
+      <c r="I481" t="s">
+        <v>6732</v>
+      </c>
+      <c r="J481" t="s">
+        <v>6733</v>
+      </c>
+      <c r="K481" t="s">
+        <v>6734</v>
+      </c>
+      <c r="L481" t="s">
+        <v>6735</v>
+      </c>
+      <c r="M481" t="s">
         <v>6736</v>
       </c>
-      <c r="B481" t="s">
+      <c r="N481" t="s">
         <v>6737</v>
       </c>
-      <c r="C481" t="s">
+      <c r="O481" t="s">
         <v>6738</v>
-      </c>
-      <c r="D481" t="s">
-        <v>6739</v>
-      </c>
-      <c r="E481" t="s">
-        <v>6740</v>
-      </c>
-      <c r="F481" t="s">
-        <v>6741</v>
-      </c>
-      <c r="G481" t="s">
-        <v>6742</v>
-      </c>
-      <c r="H481" t="s">
-        <v>6743</v>
-      </c>
-      <c r="I481" t="s">
-        <v>6744</v>
-      </c>
-      <c r="J481" t="s">
-        <v>6745</v>
-      </c>
-      <c r="K481" t="s">
-        <v>6746</v>
-      </c>
-      <c r="L481" t="s">
-        <v>6747</v>
-      </c>
-      <c r="M481" t="s">
-        <v>6748</v>
-      </c>
-      <c r="N481" t="s">
-        <v>6749</v>
-      </c>
-      <c r="O481" t="s">
-        <v>6750</v>
       </c>
     </row>
     <row r="482" spans="1:15">
       <c r="A482" t="s">
+        <v>6739</v>
+      </c>
+      <c r="B482" t="s">
+        <v>6740</v>
+      </c>
+      <c r="C482" t="s">
+        <v>6741</v>
+      </c>
+      <c r="D482" t="s">
+        <v>6742</v>
+      </c>
+      <c r="E482" t="s">
+        <v>6743</v>
+      </c>
+      <c r="F482" t="s">
+        <v>6744</v>
+      </c>
+      <c r="G482" t="s">
+        <v>6745</v>
+      </c>
+      <c r="H482" t="s">
+        <v>6746</v>
+      </c>
+      <c r="I482" t="s">
+        <v>6747</v>
+      </c>
+      <c r="J482" t="s">
+        <v>6748</v>
+      </c>
+      <c r="K482" t="s">
+        <v>6749</v>
+      </c>
+      <c r="L482" t="s">
+        <v>6750</v>
+      </c>
+      <c r="M482" t="s">
         <v>6751</v>
       </c>
-      <c r="B482" t="s">
+      <c r="N482" t="s">
         <v>6752</v>
       </c>
-      <c r="C482" t="s">
+      <c r="O482" t="s">
         <v>6753</v>
-      </c>
-      <c r="D482" t="s">
-        <v>6754</v>
-      </c>
-      <c r="E482" t="s">
-        <v>6755</v>
-      </c>
-      <c r="F482" t="s">
-        <v>6756</v>
-      </c>
-      <c r="G482" t="s">
-        <v>6757</v>
-      </c>
-      <c r="H482" t="s">
-        <v>6758</v>
-      </c>
-      <c r="I482" t="s">
-        <v>6759</v>
-      </c>
-      <c r="J482" t="s">
-        <v>6760</v>
-      </c>
-      <c r="K482" t="s">
-        <v>6761</v>
-      </c>
-      <c r="L482" t="s">
-        <v>6762</v>
-      </c>
-      <c r="M482" t="s">
-        <v>6763</v>
-      </c>
-      <c r="N482" t="s">
-        <v>6764</v>
-      </c>
-      <c r="O482" t="s">
-        <v>6765</v>
       </c>
     </row>
     <row r="483" spans="1:15">
       <c r="A483" t="s">
+        <v>6754</v>
+      </c>
+      <c r="B483" t="s">
+        <v>6755</v>
+      </c>
+      <c r="C483" t="s">
+        <v>6756</v>
+      </c>
+      <c r="D483" t="s">
+        <v>6757</v>
+      </c>
+      <c r="E483" t="s">
+        <v>6758</v>
+      </c>
+      <c r="F483" t="s">
+        <v>6759</v>
+      </c>
+      <c r="G483" t="s">
+        <v>6760</v>
+      </c>
+      <c r="H483" t="s">
+        <v>6761</v>
+      </c>
+      <c r="I483" t="s">
+        <v>6762</v>
+      </c>
+      <c r="J483" t="s">
+        <v>6763</v>
+      </c>
+      <c r="K483" t="s">
+        <v>6764</v>
+      </c>
+      <c r="L483" t="s">
+        <v>6765</v>
+      </c>
+      <c r="M483" t="s">
         <v>6766</v>
       </c>
-      <c r="B483" t="s">
+      <c r="N483" t="s">
         <v>6767</v>
       </c>
-      <c r="C483" t="s">
+      <c r="O483" t="s">
         <v>6768</v>
-      </c>
-      <c r="D483" t="s">
-        <v>6769</v>
-      </c>
-      <c r="E483" t="s">
-        <v>6770</v>
-      </c>
-      <c r="F483" t="s">
-        <v>6771</v>
-      </c>
-      <c r="G483" t="s">
-        <v>6772</v>
-      </c>
-      <c r="H483" t="s">
-        <v>6773</v>
-      </c>
-      <c r="I483" t="s">
-        <v>6774</v>
-      </c>
-      <c r="J483" t="s">
-        <v>6775</v>
-      </c>
-      <c r="K483" t="s">
-        <v>6776</v>
-      </c>
-      <c r="L483" t="s">
-        <v>6777</v>
-      </c>
-      <c r="M483" t="s">
-        <v>6778</v>
-      </c>
-      <c r="N483" t="s">
-        <v>6779</v>
-      </c>
-      <c r="O483" t="s">
-        <v>6780</v>
       </c>
     </row>
     <row r="484" spans="1:15">
       <c r="A484" t="s">
+        <v>6769</v>
+      </c>
+      <c r="B484" t="s">
+        <v>6770</v>
+      </c>
+      <c r="C484" t="s">
+        <v>6771</v>
+      </c>
+      <c r="D484" t="s">
+        <v>6772</v>
+      </c>
+      <c r="E484" t="s">
+        <v>6773</v>
+      </c>
+      <c r="F484" t="s">
+        <v>6774</v>
+      </c>
+      <c r="G484" t="s">
+        <v>6775</v>
+      </c>
+      <c r="H484" t="s">
+        <v>6776</v>
+      </c>
+      <c r="I484" t="s">
+        <v>6777</v>
+      </c>
+      <c r="J484" t="s">
+        <v>6778</v>
+      </c>
+      <c r="K484" t="s">
+        <v>6779</v>
+      </c>
+      <c r="L484" t="s">
+        <v>6780</v>
+      </c>
+      <c r="M484" t="s">
         <v>6781</v>
       </c>
-      <c r="B484" t="s">
+      <c r="N484" t="s">
         <v>6782</v>
       </c>
-      <c r="C484" t="s">
+      <c r="O484" t="s">
         <v>6783</v>
-      </c>
-      <c r="D484" t="s">
-        <v>6784</v>
-      </c>
-      <c r="E484" t="s">
-        <v>6785</v>
-      </c>
-      <c r="F484" t="s">
-        <v>6786</v>
-      </c>
-      <c r="G484" t="s">
-        <v>6787</v>
-      </c>
-      <c r="H484" t="s">
-        <v>6788</v>
-      </c>
-      <c r="I484" t="s">
-        <v>6789</v>
-      </c>
-      <c r="J484" t="s">
-        <v>6790</v>
-      </c>
-      <c r="K484" t="s">
-        <v>6791</v>
-      </c>
-      <c r="L484" t="s">
-        <v>6792</v>
-      </c>
-      <c r="M484" t="s">
-        <v>6793</v>
-      </c>
-      <c r="N484" t="s">
-        <v>6794</v>
-      </c>
-      <c r="O484" t="s">
-        <v>6795</v>
       </c>
     </row>
     <row r="485" spans="1:15">
       <c r="A485" t="s">
+        <v>6784</v>
+      </c>
+      <c r="B485" t="s">
+        <v>6785</v>
+      </c>
+      <c r="C485" t="s">
+        <v>6786</v>
+      </c>
+      <c r="D485" t="s">
+        <v>6787</v>
+      </c>
+      <c r="E485" t="s">
+        <v>6788</v>
+      </c>
+      <c r="F485" t="s">
+        <v>6789</v>
+      </c>
+      <c r="G485" t="s">
+        <v>6790</v>
+      </c>
+      <c r="H485" t="s">
+        <v>6791</v>
+      </c>
+      <c r="I485" t="s">
+        <v>6792</v>
+      </c>
+      <c r="J485" t="s">
+        <v>6793</v>
+      </c>
+      <c r="K485" t="s">
+        <v>6794</v>
+      </c>
+      <c r="L485" t="s">
+        <v>6795</v>
+      </c>
+      <c r="M485" t="s">
         <v>6796</v>
       </c>
-      <c r="B485" t="s">
+      <c r="N485" t="s">
         <v>6797</v>
       </c>
-      <c r="C485" t="s">
+      <c r="O485" t="s">
         <v>6798</v>
-      </c>
-      <c r="D485" t="s">
-        <v>6799</v>
-      </c>
-      <c r="E485" t="s">
-        <v>6800</v>
-      </c>
-      <c r="F485" t="s">
-        <v>6801</v>
-      </c>
-      <c r="G485" t="s">
-        <v>6802</v>
-      </c>
-      <c r="H485" t="s">
-        <v>6803</v>
-      </c>
-      <c r="I485" t="s">
-        <v>6804</v>
-      </c>
-      <c r="J485" t="s">
-        <v>6805</v>
-      </c>
-      <c r="K485" t="s">
-        <v>6806</v>
-      </c>
-      <c r="L485" t="s">
-        <v>6807</v>
-      </c>
-      <c r="M485" t="s">
-        <v>6808</v>
-      </c>
-      <c r="N485" t="s">
-        <v>6809</v>
-      </c>
-      <c r="O485" t="s">
-        <v>6810</v>
       </c>
     </row>
     <row r="486" spans="1:15">
       <c r="A486" t="s">
+        <v>6799</v>
+      </c>
+      <c r="B486" t="s">
+        <v>6800</v>
+      </c>
+      <c r="C486" t="s">
+        <v>6801</v>
+      </c>
+      <c r="D486" t="s">
+        <v>6802</v>
+      </c>
+      <c r="E486" t="s">
+        <v>6803</v>
+      </c>
+      <c r="F486" t="s">
+        <v>6804</v>
+      </c>
+      <c r="G486" t="s">
+        <v>6805</v>
+      </c>
+      <c r="H486" t="s">
+        <v>6806</v>
+      </c>
+      <c r="I486" t="s">
+        <v>6807</v>
+      </c>
+      <c r="J486" t="s">
+        <v>6808</v>
+      </c>
+      <c r="K486" t="s">
+        <v>6809</v>
+      </c>
+      <c r="L486" t="s">
+        <v>6810</v>
+      </c>
+      <c r="M486" t="s">
         <v>6811</v>
       </c>
-      <c r="B486" t="s">
+      <c r="N486" t="s">
         <v>6812</v>
       </c>
-      <c r="C486" t="s">
+      <c r="O486" t="s">
         <v>6813</v>
-      </c>
-      <c r="D486" t="s">
-        <v>6814</v>
-      </c>
-      <c r="E486" t="s">
-        <v>6815</v>
-      </c>
-      <c r="F486" t="s">
-        <v>6816</v>
-      </c>
-      <c r="G486" t="s">
-        <v>6817</v>
-      </c>
-      <c r="H486" t="s">
-        <v>6818</v>
-      </c>
-      <c r="I486" t="s">
-        <v>6819</v>
-      </c>
-      <c r="J486" t="s">
-        <v>6820</v>
-      </c>
-      <c r="K486" t="s">
-        <v>6821</v>
-      </c>
-      <c r="L486" t="s">
-        <v>6822</v>
-      </c>
-      <c r="M486" t="s">
-        <v>6823</v>
-      </c>
-      <c r="N486" t="s">
-        <v>6824</v>
-      </c>
-      <c r="O486" t="s">
-        <v>6825</v>
       </c>
     </row>
     <row r="487" spans="1:15">
       <c r="A487" t="s">
+        <v>6814</v>
+      </c>
+      <c r="B487" t="s">
+        <v>6815</v>
+      </c>
+      <c r="C487" t="s">
+        <v>6816</v>
+      </c>
+      <c r="D487" t="s">
+        <v>6817</v>
+      </c>
+      <c r="E487" t="s">
+        <v>6818</v>
+      </c>
+      <c r="F487" t="s">
+        <v>6819</v>
+      </c>
+      <c r="G487" t="s">
+        <v>6820</v>
+      </c>
+      <c r="H487" t="s">
+        <v>6821</v>
+      </c>
+      <c r="I487" t="s">
+        <v>6822</v>
+      </c>
+      <c r="J487" t="s">
+        <v>6823</v>
+      </c>
+      <c r="K487" t="s">
+        <v>6824</v>
+      </c>
+      <c r="L487" t="s">
+        <v>6825</v>
+      </c>
+      <c r="M487" t="s">
         <v>6826</v>
       </c>
-      <c r="B487" t="s">
+      <c r="N487" t="s">
         <v>6827</v>
       </c>
-      <c r="C487" t="s">
+      <c r="O487" t="s">
         <v>6828</v>
-      </c>
-      <c r="D487" t="s">
-        <v>6829</v>
-      </c>
-      <c r="E487" t="s">
-        <v>6830</v>
-      </c>
-      <c r="F487" t="s">
-        <v>6831</v>
-      </c>
-      <c r="G487" t="s">
-        <v>6832</v>
-      </c>
-      <c r="H487" t="s">
-        <v>6833</v>
-      </c>
-      <c r="I487" t="s">
-        <v>6834</v>
-      </c>
-      <c r="J487" t="s">
-        <v>6835</v>
-      </c>
-      <c r="K487" t="s">
-        <v>6836</v>
-      </c>
-      <c r="L487" t="s">
-        <v>6837</v>
-      </c>
-      <c r="M487" t="s">
-        <v>6838</v>
-      </c>
-      <c r="N487" t="s">
-        <v>6839</v>
-      </c>
-      <c r="O487" t="s">
-        <v>6840</v>
       </c>
     </row>
     <row r="488" spans="1:15">
       <c r="A488" t="s">
+        <v>6829</v>
+      </c>
+      <c r="B488" t="s">
+        <v>6830</v>
+      </c>
+      <c r="C488" t="s">
+        <v>6831</v>
+      </c>
+      <c r="D488" t="s">
+        <v>6832</v>
+      </c>
+      <c r="E488" t="s">
+        <v>6833</v>
+      </c>
+      <c r="F488" t="s">
+        <v>6834</v>
+      </c>
+      <c r="G488" t="s">
+        <v>6835</v>
+      </c>
+      <c r="H488" t="s">
+        <v>6836</v>
+      </c>
+      <c r="I488" t="s">
+        <v>6837</v>
+      </c>
+      <c r="J488" t="s">
+        <v>6838</v>
+      </c>
+      <c r="K488" t="s">
+        <v>6839</v>
+      </c>
+      <c r="L488" t="s">
+        <v>6840</v>
+      </c>
+      <c r="M488" t="s">
         <v>6841</v>
       </c>
-      <c r="B488" t="s">
+      <c r="N488" t="s">
         <v>6842</v>
       </c>
-      <c r="C488" t="s">
+      <c r="O488" t="s">
         <v>6843</v>
-      </c>
-      <c r="D488" t="s">
-        <v>6844</v>
-      </c>
-      <c r="E488" t="s">
-        <v>6845</v>
-      </c>
-      <c r="F488" t="s">
-        <v>6846</v>
-      </c>
-      <c r="G488" t="s">
-        <v>6847</v>
-      </c>
-      <c r="H488" t="s">
-        <v>6848</v>
-      </c>
-      <c r="I488" t="s">
-        <v>6849</v>
-      </c>
-      <c r="J488" t="s">
-        <v>6850</v>
-      </c>
-      <c r="K488" t="s">
-        <v>6851</v>
-      </c>
-      <c r="L488" t="s">
-        <v>6852</v>
-      </c>
-      <c r="M488" t="s">
-        <v>6853</v>
-      </c>
-      <c r="N488" t="s">
-        <v>6854</v>
-      </c>
-      <c r="O488" t="s">
-        <v>6855</v>
       </c>
     </row>
     <row r="489" spans="1:15">
       <c r="A489" t="s">
+        <v>6844</v>
+      </c>
+      <c r="B489" t="s">
+        <v>6845</v>
+      </c>
+      <c r="C489" t="s">
+        <v>6846</v>
+      </c>
+      <c r="D489" t="s">
+        <v>6847</v>
+      </c>
+      <c r="E489" t="s">
+        <v>6848</v>
+      </c>
+      <c r="F489" t="s">
+        <v>6849</v>
+      </c>
+      <c r="G489" t="s">
+        <v>6850</v>
+      </c>
+      <c r="H489" t="s">
+        <v>6851</v>
+      </c>
+      <c r="I489" t="s">
+        <v>6852</v>
+      </c>
+      <c r="J489" t="s">
+        <v>6853</v>
+      </c>
+      <c r="K489" t="s">
+        <v>6854</v>
+      </c>
+      <c r="L489" t="s">
+        <v>6855</v>
+      </c>
+      <c r="M489" t="s">
         <v>6856</v>
       </c>
-      <c r="B489" t="s">
+      <c r="N489" t="s">
         <v>6857</v>
       </c>
-      <c r="C489" t="s">
+      <c r="O489" t="s">
         <v>6858</v>
-      </c>
-      <c r="D489" t="s">
-        <v>6859</v>
-      </c>
-      <c r="E489" t="s">
-        <v>6860</v>
-      </c>
-      <c r="F489" t="s">
-        <v>6861</v>
-      </c>
-      <c r="G489" t="s">
-        <v>6862</v>
-      </c>
-      <c r="H489" t="s">
-        <v>6863</v>
-      </c>
-      <c r="I489" t="s">
-        <v>6864</v>
-      </c>
-      <c r="J489" t="s">
-        <v>6865</v>
-      </c>
-      <c r="K489" t="s">
-        <v>6866</v>
-      </c>
-      <c r="L489" t="s">
-        <v>6867</v>
-      </c>
-      <c r="M489" t="s">
-        <v>6868</v>
-      </c>
-      <c r="N489" t="s">
-        <v>6869</v>
-      </c>
-      <c r="O489" t="s">
-        <v>6870</v>
       </c>
     </row>
     <row r="490" spans="1:15">
       <c r="A490" t="s">
+        <v>6859</v>
+      </c>
+      <c r="B490" t="s">
+        <v>6860</v>
+      </c>
+      <c r="C490" t="s">
+        <v>6861</v>
+      </c>
+      <c r="D490" t="s">
+        <v>6862</v>
+      </c>
+      <c r="E490" t="s">
+        <v>6863</v>
+      </c>
+      <c r="F490" t="s">
+        <v>6864</v>
+      </c>
+      <c r="G490" t="s">
+        <v>6865</v>
+      </c>
+      <c r="H490" t="s">
+        <v>6866</v>
+      </c>
+      <c r="I490" t="s">
+        <v>6867</v>
+      </c>
+      <c r="J490" t="s">
+        <v>6868</v>
+      </c>
+      <c r="K490" t="s">
+        <v>6869</v>
+      </c>
+      <c r="L490" t="s">
+        <v>6870</v>
+      </c>
+      <c r="M490" t="s">
         <v>6871</v>
       </c>
-      <c r="B490" t="s">
+      <c r="N490" t="s">
         <v>6872</v>
       </c>
-      <c r="C490" t="s">
+      <c r="O490" t="s">
         <v>6873</v>
-      </c>
-      <c r="D490" t="s">
-        <v>6874</v>
-      </c>
-      <c r="E490" t="s">
-        <v>6875</v>
-      </c>
-      <c r="F490" t="s">
-        <v>6876</v>
-      </c>
-      <c r="G490" t="s">
-        <v>6877</v>
-      </c>
-      <c r="H490" t="s">
-        <v>6878</v>
-      </c>
-      <c r="I490" t="s">
-        <v>6879</v>
-      </c>
-      <c r="J490" t="s">
-        <v>6880</v>
-      </c>
-      <c r="K490" t="s">
-        <v>6881</v>
-      </c>
-      <c r="L490" t="s">
-        <v>6882</v>
-      </c>
-      <c r="M490" t="s">
-        <v>6883</v>
-      </c>
-      <c r="N490" t="s">
-        <v>6884</v>
-      </c>
-      <c r="O490" t="s">
-        <v>6885</v>
       </c>
     </row>
     <row r="491" spans="1:15">
       <c r="A491" t="s">
+        <v>6874</v>
+      </c>
+      <c r="B491" t="s">
+        <v>6875</v>
+      </c>
+      <c r="C491" t="s">
+        <v>6876</v>
+      </c>
+      <c r="D491" t="s">
+        <v>6877</v>
+      </c>
+      <c r="E491" t="s">
+        <v>6878</v>
+      </c>
+      <c r="F491" t="s">
+        <v>6879</v>
+      </c>
+      <c r="G491" t="s">
+        <v>6880</v>
+      </c>
+      <c r="H491" t="s">
+        <v>6881</v>
+      </c>
+      <c r="I491" t="s">
+        <v>6882</v>
+      </c>
+      <c r="J491" t="s">
+        <v>6883</v>
+      </c>
+      <c r="K491" t="s">
+        <v>6884</v>
+      </c>
+      <c r="L491" t="s">
+        <v>6885</v>
+      </c>
+      <c r="M491" t="s">
         <v>6886</v>
       </c>
-      <c r="B491" t="s">
+      <c r="N491" t="s">
         <v>6887</v>
       </c>
-      <c r="C491" t="s">
+      <c r="O491" t="s">
         <v>6888</v>
-      </c>
-      <c r="D491" t="s">
-        <v>6889</v>
-      </c>
-      <c r="E491" t="s">
-        <v>6890</v>
-      </c>
-      <c r="F491" t="s">
-        <v>6891</v>
-      </c>
-      <c r="G491" t="s">
-        <v>6892</v>
-      </c>
-      <c r="H491" t="s">
-        <v>6893</v>
-      </c>
-      <c r="I491" t="s">
-        <v>6894</v>
-      </c>
-      <c r="J491" t="s">
-        <v>6895</v>
-      </c>
-      <c r="K491" t="s">
-        <v>6896</v>
-      </c>
-      <c r="L491" t="s">
-        <v>6897</v>
-      </c>
-      <c r="M491" t="s">
-        <v>6898</v>
-      </c>
-      <c r="N491" t="s">
-        <v>6899</v>
-      </c>
-      <c r="O491" t="s">
-        <v>6900</v>
       </c>
     </row>
     <row r="492" spans="1:15">
       <c r="A492" t="s">
+        <v>6889</v>
+      </c>
+      <c r="B492" t="s">
+        <v>6890</v>
+      </c>
+      <c r="C492" t="s">
+        <v>6891</v>
+      </c>
+      <c r="D492" t="s">
+        <v>6892</v>
+      </c>
+      <c r="E492" t="s">
+        <v>6893</v>
+      </c>
+      <c r="F492" t="s">
+        <v>6894</v>
+      </c>
+      <c r="G492" t="s">
+        <v>6895</v>
+      </c>
+      <c r="H492" t="s">
+        <v>6896</v>
+      </c>
+      <c r="I492" t="s">
+        <v>6897</v>
+      </c>
+      <c r="J492" t="s">
+        <v>6898</v>
+      </c>
+      <c r="K492" t="s">
+        <v>6899</v>
+      </c>
+      <c r="L492" t="s">
+        <v>6900</v>
+      </c>
+      <c r="M492" t="s">
         <v>6901</v>
       </c>
-      <c r="B492" t="s">
+      <c r="N492" t="s">
         <v>6902</v>
       </c>
-      <c r="C492" t="s">
+      <c r="O492" t="s">
         <v>6903</v>
-      </c>
-      <c r="D492" t="s">
-        <v>6904</v>
-      </c>
-      <c r="E492" t="s">
-        <v>6905</v>
-      </c>
-      <c r="F492" t="s">
-        <v>6906</v>
-      </c>
-      <c r="G492" t="s">
-        <v>6907</v>
-      </c>
-      <c r="H492" t="s">
-        <v>6908</v>
-      </c>
-      <c r="I492" t="s">
-        <v>6909</v>
-      </c>
-      <c r="J492" t="s">
-        <v>6910</v>
-      </c>
-      <c r="K492" t="s">
-        <v>6911</v>
-      </c>
-      <c r="L492" t="s">
-        <v>6912</v>
-      </c>
-      <c r="M492" t="s">
-        <v>6913</v>
-      </c>
-      <c r="N492" t="s">
-        <v>6914</v>
-      </c>
-      <c r="O492" t="s">
-        <v>6915</v>
       </c>
     </row>
     <row r="493" spans="1:15">
       <c r="A493" t="s">
+        <v>6904</v>
+      </c>
+      <c r="B493" t="s">
+        <v>6905</v>
+      </c>
+      <c r="C493" t="s">
+        <v>6906</v>
+      </c>
+      <c r="D493" t="s">
+        <v>6907</v>
+      </c>
+      <c r="E493" t="s">
+        <v>6908</v>
+      </c>
+      <c r="F493" t="s">
+        <v>6909</v>
+      </c>
+      <c r="G493" t="s">
+        <v>6910</v>
+      </c>
+      <c r="H493" t="s">
+        <v>6911</v>
+      </c>
+      <c r="I493" t="s">
+        <v>6912</v>
+      </c>
+      <c r="J493" t="s">
+        <v>6913</v>
+      </c>
+      <c r="K493" t="s">
+        <v>6914</v>
+      </c>
+      <c r="L493" t="s">
+        <v>6915</v>
+      </c>
+      <c r="M493" t="s">
         <v>6916</v>
       </c>
-      <c r="B493" t="s">
+      <c r="N493" t="s">
         <v>6917</v>
       </c>
-      <c r="C493" t="s">
+      <c r="O493" t="s">
         <v>6918</v>
-      </c>
-      <c r="D493" t="s">
-        <v>6919</v>
-      </c>
-      <c r="E493" t="s">
-        <v>6920</v>
-      </c>
-      <c r="F493" t="s">
-        <v>6921</v>
-      </c>
-      <c r="G493" t="s">
-        <v>6922</v>
-      </c>
-      <c r="H493" t="s">
-        <v>6923</v>
-      </c>
-      <c r="I493" t="s">
-        <v>6924</v>
-      </c>
-      <c r="J493" t="s">
-        <v>6925</v>
-      </c>
-      <c r="K493" t="s">
-        <v>6926</v>
-      </c>
-      <c r="L493" t="s">
-        <v>6927</v>
-      </c>
-      <c r="M493" t="s">
-        <v>6928</v>
-      </c>
-      <c r="N493" t="s">
-        <v>6929</v>
-      </c>
-      <c r="O493" t="s">
-        <v>6930</v>
       </c>
     </row>
     <row r="494" spans="1:15">
       <c r="A494" t="s">
+        <v>6919</v>
+      </c>
+      <c r="B494" t="s">
+        <v>6920</v>
+      </c>
+      <c r="C494" t="s">
+        <v>6921</v>
+      </c>
+      <c r="D494" t="s">
+        <v>6922</v>
+      </c>
+      <c r="E494" t="s">
+        <v>6923</v>
+      </c>
+      <c r="F494" t="s">
+        <v>6924</v>
+      </c>
+      <c r="G494" t="s">
+        <v>6925</v>
+      </c>
+      <c r="H494" t="s">
+        <v>6926</v>
+      </c>
+      <c r="I494" t="s">
+        <v>6927</v>
+      </c>
+      <c r="J494" t="s">
+        <v>6928</v>
+      </c>
+      <c r="K494" t="s">
+        <v>6929</v>
+      </c>
+      <c r="L494" t="s">
+        <v>6930</v>
+      </c>
+      <c r="M494" t="s">
         <v>6931</v>
       </c>
-      <c r="B494" t="s">
+      <c r="N494" t="s">
         <v>6932</v>
       </c>
-      <c r="C494" t="s">
+      <c r="O494" t="s">
         <v>6933</v>
-      </c>
-      <c r="D494" t="s">
-        <v>6934</v>
-      </c>
-      <c r="E494" t="s">
-        <v>6935</v>
-      </c>
-      <c r="F494" t="s">
-        <v>6936</v>
-      </c>
-      <c r="G494" t="s">
-        <v>6937</v>
-      </c>
-      <c r="H494" t="s">
-        <v>6938</v>
-      </c>
-      <c r="I494" t="s">
-        <v>6939</v>
-      </c>
-      <c r="J494" t="s">
-        <v>6940</v>
-      </c>
-      <c r="K494" t="s">
-        <v>6941</v>
-      </c>
-      <c r="L494" t="s">
-        <v>6942</v>
-      </c>
-      <c r="M494" t="s">
-        <v>6943</v>
-      </c>
-      <c r="N494" t="s">
-        <v>6944</v>
-      </c>
-      <c r="O494" t="s">
-        <v>6945</v>
       </c>
     </row>
     <row r="495" spans="1:15">
       <c r="A495" t="s">
+        <v>6934</v>
+      </c>
+      <c r="B495" t="s">
+        <v>6935</v>
+      </c>
+      <c r="C495" t="s">
+        <v>6936</v>
+      </c>
+      <c r="D495" t="s">
+        <v>6937</v>
+      </c>
+      <c r="E495" t="s">
+        <v>6938</v>
+      </c>
+      <c r="F495" t="s">
+        <v>6939</v>
+      </c>
+      <c r="G495" t="s">
+        <v>6940</v>
+      </c>
+      <c r="H495" t="s">
+        <v>6941</v>
+      </c>
+      <c r="I495" t="s">
+        <v>6942</v>
+      </c>
+      <c r="J495" t="s">
+        <v>6943</v>
+      </c>
+      <c r="K495" t="s">
+        <v>6944</v>
+      </c>
+      <c r="L495" t="s">
+        <v>6945</v>
+      </c>
+      <c r="M495" t="s">
         <v>6946</v>
       </c>
-      <c r="B495" t="s">
+      <c r="N495" t="s">
         <v>6947</v>
       </c>
-      <c r="C495" t="s">
+      <c r="O495" t="s">
         <v>6948</v>
-      </c>
-      <c r="D495" t="s">
-        <v>6949</v>
-      </c>
-      <c r="E495" t="s">
-        <v>6950</v>
-      </c>
-      <c r="F495" t="s">
-        <v>6951</v>
-      </c>
-      <c r="G495" t="s">
-        <v>6952</v>
-      </c>
-      <c r="H495" t="s">
-        <v>6953</v>
-      </c>
-      <c r="I495" t="s">
-        <v>6954</v>
-      </c>
-      <c r="J495" t="s">
-        <v>6955</v>
-      </c>
-      <c r="K495" t="s">
-        <v>6956</v>
-      </c>
-      <c r="L495" t="s">
-        <v>6957</v>
-      </c>
-      <c r="M495" t="s">
-        <v>6958</v>
-      </c>
-      <c r="N495" t="s">
-        <v>6959</v>
-      </c>
-      <c r="O495" t="s">
-        <v>6960</v>
       </c>
     </row>
     <row r="496" spans="1:15">
       <c r="A496" t="s">
+        <v>6949</v>
+      </c>
+      <c r="B496" t="s">
+        <v>6950</v>
+      </c>
+      <c r="C496" t="s">
+        <v>6951</v>
+      </c>
+      <c r="D496" t="s">
+        <v>6952</v>
+      </c>
+      <c r="E496" t="s">
+        <v>6953</v>
+      </c>
+      <c r="F496" t="s">
+        <v>6954</v>
+      </c>
+      <c r="G496" t="s">
+        <v>6955</v>
+      </c>
+      <c r="H496" t="s">
+        <v>6956</v>
+      </c>
+      <c r="I496" t="s">
+        <v>6957</v>
+      </c>
+      <c r="J496" t="s">
+        <v>6958</v>
+      </c>
+      <c r="K496" t="s">
+        <v>6959</v>
+      </c>
+      <c r="L496" t="s">
+        <v>6960</v>
+      </c>
+      <c r="M496" t="s">
         <v>6961</v>
       </c>
-      <c r="B496" t="s">
+      <c r="N496" t="s">
         <v>6962</v>
       </c>
-      <c r="C496" t="s">
+      <c r="O496" t="s">
         <v>6963</v>
-      </c>
-      <c r="D496" t="s">
-        <v>6964</v>
-      </c>
-      <c r="E496" t="s">
-        <v>6965</v>
-      </c>
-      <c r="F496" t="s">
-        <v>6966</v>
-      </c>
-      <c r="G496" t="s">
-        <v>6967</v>
-      </c>
-      <c r="H496" t="s">
-        <v>6968</v>
-      </c>
-      <c r="I496" t="s">
-        <v>6969</v>
-      </c>
-      <c r="J496" t="s">
-        <v>6970</v>
-      </c>
-      <c r="K496" t="s">
-        <v>6971</v>
-      </c>
-      <c r="L496" t="s">
-        <v>6972</v>
-      </c>
-      <c r="M496" t="s">
-        <v>6973</v>
-      </c>
-      <c r="N496" t="s">
-        <v>6974</v>
-      </c>
-      <c r="O496" t="s">
-        <v>6975</v>
       </c>
     </row>
     <row r="497" spans="1:15">
       <c r="A497" t="s">
+        <v>6964</v>
+      </c>
+      <c r="B497" t="s">
+        <v>6965</v>
+      </c>
+      <c r="C497" t="s">
+        <v>6966</v>
+      </c>
+      <c r="D497" t="s">
+        <v>6967</v>
+      </c>
+      <c r="E497" t="s">
+        <v>6968</v>
+      </c>
+      <c r="F497" t="s">
+        <v>6969</v>
+      </c>
+      <c r="G497" t="s">
+        <v>6970</v>
+      </c>
+      <c r="H497" t="s">
+        <v>6971</v>
+      </c>
+      <c r="I497" t="s">
+        <v>6972</v>
+      </c>
+      <c r="J497" t="s">
+        <v>6973</v>
+      </c>
+      <c r="K497" t="s">
+        <v>6974</v>
+      </c>
+      <c r="L497" t="s">
+        <v>6975</v>
+      </c>
+      <c r="M497" t="s">
         <v>6976</v>
       </c>
-      <c r="B497" t="s">
+      <c r="N497" t="s">
         <v>6977</v>
       </c>
-      <c r="C497" t="s">
-        <v>6978</v>
-      </c>
-      <c r="D497" t="s">
-        <v>6979</v>
-      </c>
-      <c r="E497" t="s">
-        <v>6980</v>
-      </c>
-      <c r="F497" t="s">
-        <v>6981</v>
-      </c>
-      <c r="G497" t="s">
-        <v>6982</v>
-      </c>
-      <c r="H497" t="s">
-        <v>6983</v>
-      </c>
-      <c r="I497" t="s">
-        <v>6984</v>
-      </c>
-      <c r="J497" t="s">
-        <v>6985</v>
-      </c>
-      <c r="K497" t="s">
-        <v>6986</v>
-      </c>
-      <c r="L497" t="s">
-        <v>6987</v>
-      </c>
-      <c r="M497" t="s">
-        <v>6988</v>
-      </c>
-      <c r="N497" t="s">
-        <v>6989</v>
-      </c>
       <c r="O497" t="s">
-        <v>6977</v>
+        <v>6965</v>
       </c>
     </row>
     <row r="498" spans="1:15">
       <c r="A498" t="s">
-        <v>6990</v>
+        <v>6978</v>
       </c>
       <c r="B498" t="s">
-        <v>6991</v>
+        <v>6979</v>
       </c>
       <c r="C498" t="s">
-        <v>6992</v>
+        <v>6980</v>
       </c>
       <c r="D498" t="s">
-        <v>6992</v>
+        <v>6980</v>
       </c>
       <c r="E498" t="s">
-        <v>6992</v>
+        <v>6980</v>
       </c>
       <c r="F498" t="s">
-        <v>6992</v>
+        <v>6980</v>
       </c>
       <c r="G498" t="s">
-        <v>6992</v>
+        <v>6980</v>
       </c>
       <c r="H498" t="s">
-        <v>6992</v>
+        <v>6980</v>
       </c>
       <c r="I498" t="s">
-        <v>6992</v>
+        <v>6980</v>
       </c>
       <c r="J498" t="s">
-        <v>6992</v>
+        <v>6980</v>
       </c>
       <c r="K498" t="s">
-        <v>6992</v>
+        <v>6980</v>
       </c>
       <c r="L498" t="s">
-        <v>6992</v>
+        <v>6980</v>
       </c>
       <c r="M498" t="s">
-        <v>6992</v>
+        <v>6980</v>
       </c>
       <c r="N498" t="s">
-        <v>6992</v>
+        <v>6980</v>
       </c>
       <c r="O498" t="s">
-        <v>6992</v>
+        <v>6980</v>
       </c>
     </row>
     <row r="499" spans="1:15">
       <c r="A499" t="s">
+        <v>6981</v>
+      </c>
+      <c r="B499" t="s">
+        <v>6982</v>
+      </c>
+      <c r="C499" t="s">
+        <v>6983</v>
+      </c>
+      <c r="D499" t="s">
+        <v>6984</v>
+      </c>
+      <c r="E499" t="s">
+        <v>6985</v>
+      </c>
+      <c r="F499" t="s">
+        <v>6986</v>
+      </c>
+      <c r="G499" t="s">
+        <v>6987</v>
+      </c>
+      <c r="H499" t="s">
+        <v>6988</v>
+      </c>
+      <c r="I499" t="s">
+        <v>6989</v>
+      </c>
+      <c r="J499" t="s">
+        <v>6990</v>
+      </c>
+      <c r="K499" t="s">
+        <v>6991</v>
+      </c>
+      <c r="L499" t="s">
+        <v>6992</v>
+      </c>
+      <c r="M499" t="s">
         <v>6993</v>
       </c>
-      <c r="B499" t="s">
+      <c r="N499" t="s">
         <v>6994</v>
       </c>
-      <c r="C499" t="s">
+      <c r="O499" t="s">
         <v>6995</v>
-      </c>
-      <c r="D499" t="s">
-        <v>6996</v>
-      </c>
-      <c r="E499" t="s">
-        <v>6997</v>
-      </c>
-      <c r="F499" t="s">
-        <v>6998</v>
-      </c>
-      <c r="G499" t="s">
-        <v>6999</v>
-      </c>
-      <c r="H499" t="s">
-        <v>7000</v>
-      </c>
-      <c r="I499" t="s">
-        <v>7001</v>
-      </c>
-      <c r="J499" t="s">
-        <v>7002</v>
-      </c>
-      <c r="K499" t="s">
-        <v>7003</v>
-      </c>
-      <c r="L499" t="s">
-        <v>7004</v>
-      </c>
-      <c r="M499" t="s">
-        <v>7005</v>
-      </c>
-      <c r="N499" t="s">
-        <v>7006</v>
-      </c>
-      <c r="O499" t="s">
-        <v>7007</v>
       </c>
     </row>
     <row r="500" spans="1:15">
       <c r="A500" t="s">
+        <v>6996</v>
+      </c>
+      <c r="B500" t="s">
+        <v>6997</v>
+      </c>
+      <c r="C500" t="s">
+        <v>6998</v>
+      </c>
+      <c r="D500" t="s">
+        <v>6999</v>
+      </c>
+      <c r="E500" t="s">
+        <v>7000</v>
+      </c>
+      <c r="F500" t="s">
+        <v>7001</v>
+      </c>
+      <c r="G500" t="s">
+        <v>7002</v>
+      </c>
+      <c r="H500" t="s">
+        <v>7003</v>
+      </c>
+      <c r="I500" t="s">
+        <v>7004</v>
+      </c>
+      <c r="J500" t="s">
+        <v>7005</v>
+      </c>
+      <c r="K500" t="s">
+        <v>7006</v>
+      </c>
+      <c r="L500" t="s">
+        <v>7007</v>
+      </c>
+      <c r="M500" t="s">
         <v>7008</v>
       </c>
-      <c r="B500" t="s">
+      <c r="N500" t="s">
         <v>7009</v>
       </c>
-      <c r="C500" t="s">
+      <c r="O500" t="s">
         <v>7010</v>
-      </c>
-      <c r="D500" t="s">
-        <v>7011</v>
-      </c>
-      <c r="E500" t="s">
-        <v>7012</v>
-      </c>
-      <c r="F500" t="s">
-        <v>7013</v>
-      </c>
-      <c r="G500" t="s">
-        <v>7014</v>
-      </c>
-      <c r="H500" t="s">
-        <v>7015</v>
-      </c>
-      <c r="I500" t="s">
-        <v>7016</v>
-      </c>
-      <c r="J500" t="s">
-        <v>7017</v>
-      </c>
-      <c r="K500" t="s">
-        <v>7018</v>
-      </c>
-      <c r="L500" t="s">
-        <v>7019</v>
-      </c>
-      <c r="M500" t="s">
-        <v>7020</v>
-      </c>
-      <c r="N500" t="s">
-        <v>7021</v>
-      </c>
-      <c r="O500" t="s">
-        <v>7022</v>
       </c>
     </row>
     <row r="501" spans="1:15">
       <c r="A501" t="s">
-        <v>7023</v>
+        <v>7011</v>
       </c>
       <c r="B501" t="s">
-        <v>7024</v>
+        <v>7012</v>
       </c>
       <c r="C501" t="s">
-        <v>7025</v>
+        <v>7013</v>
       </c>
       <c r="D501" t="s">
-        <v>7025</v>
+        <v>7013</v>
       </c>
       <c r="E501" t="s">
-        <v>7025</v>
+        <v>7013</v>
       </c>
       <c r="F501" t="s">
-        <v>7025</v>
+        <v>7013</v>
       </c>
       <c r="G501" t="s">
-        <v>7025</v>
+        <v>7013</v>
       </c>
       <c r="H501" t="s">
-        <v>7025</v>
+        <v>7013</v>
       </c>
       <c r="I501" t="s">
-        <v>7025</v>
+        <v>7013</v>
       </c>
       <c r="J501" t="s">
-        <v>7025</v>
+        <v>7013</v>
       </c>
       <c r="K501" t="s">
-        <v>7025</v>
+        <v>7013</v>
       </c>
       <c r="L501" t="s">
-        <v>7025</v>
+        <v>7013</v>
       </c>
       <c r="M501" t="s">
-        <v>7025</v>
+        <v>7013</v>
       </c>
       <c r="N501" t="s">
-        <v>7025</v>
+        <v>7013</v>
       </c>
       <c r="O501" t="s">
-        <v>7025</v>
+        <v>7013</v>
       </c>
     </row>
     <row r="502" spans="1:15">
       <c r="A502" t="s">
+        <v>7014</v>
+      </c>
+      <c r="B502" t="s">
+        <v>7015</v>
+      </c>
+      <c r="C502" t="s">
+        <v>7016</v>
+      </c>
+      <c r="D502" t="s">
+        <v>7017</v>
+      </c>
+      <c r="E502" t="s">
+        <v>7018</v>
+      </c>
+      <c r="F502" t="s">
+        <v>7019</v>
+      </c>
+      <c r="G502" t="s">
+        <v>7020</v>
+      </c>
+      <c r="H502" t="s">
+        <v>7021</v>
+      </c>
+      <c r="I502" t="s">
+        <v>7022</v>
+      </c>
+      <c r="J502" t="s">
+        <v>7023</v>
+      </c>
+      <c r="K502" t="s">
+        <v>7024</v>
+      </c>
+      <c r="L502" t="s">
+        <v>7025</v>
+      </c>
+      <c r="M502" t="s">
         <v>7026</v>
       </c>
-      <c r="B502" t="s">
+      <c r="N502" t="s">
         <v>7027</v>
       </c>
-      <c r="C502" t="s">
-        <v>7028</v>
-      </c>
-      <c r="D502" t="s">
-        <v>7029</v>
-      </c>
-      <c r="E502" t="s">
-        <v>7030</v>
-      </c>
-      <c r="F502" t="s">
-        <v>7031</v>
-      </c>
-      <c r="G502" t="s">
-        <v>7032</v>
-      </c>
-      <c r="H502" t="s">
-        <v>7033</v>
-      </c>
-      <c r="I502" t="s">
-        <v>7034</v>
-      </c>
-      <c r="J502" t="s">
-        <v>7035</v>
-      </c>
-      <c r="K502" t="s">
-        <v>7036</v>
-      </c>
-      <c r="L502" t="s">
-        <v>7037</v>
-      </c>
-      <c r="M502" t="s">
-        <v>7038</v>
-      </c>
-      <c r="N502" t="s">
-        <v>7039</v>
-      </c>
       <c r="O502" t="s">
-        <v>7027</v>
+        <v>7015</v>
       </c>
     </row>
     <row r="503" spans="1:15">
       <c r="A503" t="s">
+        <v>7028</v>
+      </c>
+      <c r="B503" t="s">
+        <v>7029</v>
+      </c>
+      <c r="C503" t="s">
+        <v>7030</v>
+      </c>
+      <c r="D503" t="s">
+        <v>7031</v>
+      </c>
+      <c r="E503" t="s">
+        <v>7032</v>
+      </c>
+      <c r="F503" t="s">
+        <v>7033</v>
+      </c>
+      <c r="G503" t="s">
+        <v>7034</v>
+      </c>
+      <c r="H503" t="s">
+        <v>7035</v>
+      </c>
+      <c r="I503" t="s">
+        <v>7036</v>
+      </c>
+      <c r="J503" t="s">
+        <v>7037</v>
+      </c>
+      <c r="K503" t="s">
+        <v>7038</v>
+      </c>
+      <c r="L503" t="s">
+        <v>7039</v>
+      </c>
+      <c r="M503" t="s">
         <v>7040</v>
       </c>
-      <c r="B503" t="s">
+      <c r="N503" t="s">
         <v>7041</v>
       </c>
-      <c r="C503" t="s">
+      <c r="O503" t="s">
         <v>7042</v>
-      </c>
-      <c r="D503" t="s">
-        <v>7043</v>
-      </c>
-      <c r="E503" t="s">
-        <v>7044</v>
-      </c>
-      <c r="F503" t="s">
-        <v>7045</v>
-      </c>
-      <c r="G503" t="s">
-        <v>7046</v>
-      </c>
-      <c r="H503" t="s">
-        <v>7047</v>
-      </c>
-      <c r="I503" t="s">
-        <v>7048</v>
-      </c>
-      <c r="J503" t="s">
-        <v>7049</v>
-      </c>
-      <c r="K503" t="s">
-        <v>7050</v>
-      </c>
-      <c r="L503" t="s">
-        <v>7051</v>
-      </c>
-      <c r="M503" t="s">
-        <v>7052</v>
-      </c>
-      <c r="N503" t="s">
-        <v>7053</v>
-      </c>
-      <c r="O503" t="s">
-        <v>7054</v>
       </c>
     </row>
     <row r="504" spans="1:15">
       <c r="A504" t="s">
+        <v>7043</v>
+      </c>
+      <c r="B504" t="s">
+        <v>7044</v>
+      </c>
+      <c r="C504" t="s">
+        <v>7045</v>
+      </c>
+      <c r="D504" t="s">
+        <v>7046</v>
+      </c>
+      <c r="E504" t="s">
+        <v>7047</v>
+      </c>
+      <c r="F504" t="s">
+        <v>7048</v>
+      </c>
+      <c r="G504" t="s">
+        <v>7049</v>
+      </c>
+      <c r="H504" t="s">
+        <v>7050</v>
+      </c>
+      <c r="I504" t="s">
+        <v>7051</v>
+      </c>
+      <c r="J504" t="s">
+        <v>7052</v>
+      </c>
+      <c r="K504" t="s">
+        <v>7053</v>
+      </c>
+      <c r="L504" t="s">
+        <v>7054</v>
+      </c>
+      <c r="M504" t="s">
         <v>7055</v>
       </c>
-      <c r="B504" t="s">
+      <c r="N504" t="s">
         <v>7056</v>
       </c>
-      <c r="C504" t="s">
+      <c r="O504" t="s">
         <v>7057</v>
-      </c>
-      <c r="D504" t="s">
-        <v>7058</v>
-      </c>
-      <c r="E504" t="s">
-        <v>7059</v>
-      </c>
-      <c r="F504" t="s">
-        <v>7060</v>
-      </c>
-      <c r="G504" t="s">
-        <v>7061</v>
-      </c>
-      <c r="H504" t="s">
-        <v>7062</v>
-      </c>
-      <c r="I504" t="s">
-        <v>7063</v>
-      </c>
-      <c r="J504" t="s">
-        <v>7064</v>
-      </c>
-      <c r="K504" t="s">
-        <v>7065</v>
-      </c>
-      <c r="L504" t="s">
-        <v>7066</v>
-      </c>
-      <c r="M504" t="s">
-        <v>7067</v>
-      </c>
-      <c r="N504" t="s">
-        <v>7068</v>
-      </c>
-      <c r="O504" t="s">
-        <v>7069</v>
       </c>
     </row>
     <row r="505" spans="1:15">
       <c r="A505" t="s">
+        <v>7058</v>
+      </c>
+      <c r="B505" t="s">
+        <v>7059</v>
+      </c>
+      <c r="C505" t="s">
+        <v>7060</v>
+      </c>
+      <c r="D505" t="s">
+        <v>7061</v>
+      </c>
+      <c r="E505" t="s">
+        <v>7062</v>
+      </c>
+      <c r="F505" t="s">
+        <v>7063</v>
+      </c>
+      <c r="G505" t="s">
+        <v>7064</v>
+      </c>
+      <c r="H505" t="s">
+        <v>7065</v>
+      </c>
+      <c r="I505" t="s">
+        <v>7066</v>
+      </c>
+      <c r="J505" t="s">
+        <v>7067</v>
+      </c>
+      <c r="K505" t="s">
+        <v>7068</v>
+      </c>
+      <c r="L505" t="s">
+        <v>7069</v>
+      </c>
+      <c r="M505" t="s">
         <v>7070</v>
       </c>
-      <c r="B505" t="s">
+      <c r="N505" t="s">
         <v>7071</v>
       </c>
-      <c r="C505" t="s">
+      <c r="O505" t="s">
         <v>7072</v>
-      </c>
-      <c r="D505" t="s">
-        <v>7073</v>
-      </c>
-      <c r="E505" t="s">
-        <v>7074</v>
-      </c>
-      <c r="F505" t="s">
-        <v>7075</v>
-      </c>
-      <c r="G505" t="s">
-        <v>7076</v>
-      </c>
-      <c r="H505" t="s">
-        <v>7077</v>
-      </c>
-      <c r="I505" t="s">
-        <v>7078</v>
-      </c>
-      <c r="J505" t="s">
-        <v>7079</v>
-      </c>
-      <c r="K505" t="s">
-        <v>7080</v>
-      </c>
-      <c r="L505" t="s">
-        <v>7081</v>
-      </c>
-      <c r="M505" t="s">
-        <v>7082</v>
-      </c>
-      <c r="N505" t="s">
-        <v>7083</v>
-      </c>
-      <c r="O505" t="s">
-        <v>7084</v>
       </c>
     </row>
     <row r="506" spans="1:15">
       <c r="A506" t="s">
+        <v>7073</v>
+      </c>
+      <c r="B506" t="s">
+        <v>7074</v>
+      </c>
+      <c r="C506" t="s">
+        <v>7075</v>
+      </c>
+      <c r="D506" t="s">
+        <v>7076</v>
+      </c>
+      <c r="E506" t="s">
+        <v>7077</v>
+      </c>
+      <c r="F506" t="s">
+        <v>7078</v>
+      </c>
+      <c r="G506" t="s">
+        <v>7079</v>
+      </c>
+      <c r="H506" t="s">
+        <v>7080</v>
+      </c>
+      <c r="I506" t="s">
+        <v>7081</v>
+      </c>
+      <c r="J506" t="s">
+        <v>7082</v>
+      </c>
+      <c r="K506" t="s">
+        <v>7083</v>
+      </c>
+      <c r="L506" t="s">
+        <v>7084</v>
+      </c>
+      <c r="M506" t="s">
         <v>7085</v>
       </c>
-      <c r="B506" t="s">
+      <c r="N506" t="s">
         <v>7086</v>
       </c>
-      <c r="C506" t="s">
+      <c r="O506" t="s">
         <v>7087</v>
-      </c>
-      <c r="D506" t="s">
-        <v>7088</v>
-      </c>
-      <c r="E506" t="s">
-        <v>7089</v>
-      </c>
-      <c r="F506" t="s">
-        <v>7090</v>
-      </c>
-      <c r="G506" t="s">
-        <v>7091</v>
-      </c>
-      <c r="H506" t="s">
-        <v>7092</v>
-      </c>
-      <c r="I506" t="s">
-        <v>7093</v>
-      </c>
-      <c r="J506" t="s">
-        <v>7094</v>
-      </c>
-      <c r="K506" t="s">
-        <v>7095</v>
-      </c>
-      <c r="L506" t="s">
-        <v>7096</v>
-      </c>
-      <c r="M506" t="s">
-        <v>7097</v>
-      </c>
-      <c r="N506" t="s">
-        <v>7098</v>
-      </c>
-      <c r="O506" t="s">
-        <v>7099</v>
       </c>
     </row>
     <row r="507" spans="1:15">
       <c r="A507" t="s">
+        <v>7088</v>
+      </c>
+      <c r="B507" t="s">
+        <v>7089</v>
+      </c>
+      <c r="C507" t="s">
+        <v>7090</v>
+      </c>
+      <c r="D507" t="s">
+        <v>7091</v>
+      </c>
+      <c r="E507" t="s">
+        <v>7092</v>
+      </c>
+      <c r="F507" t="s">
+        <v>7093</v>
+      </c>
+      <c r="G507" t="s">
+        <v>7094</v>
+      </c>
+      <c r="H507" t="s">
+        <v>7095</v>
+      </c>
+      <c r="I507" t="s">
+        <v>7096</v>
+      </c>
+      <c r="J507" t="s">
+        <v>7097</v>
+      </c>
+      <c r="K507" t="s">
+        <v>7098</v>
+      </c>
+      <c r="L507" t="s">
+        <v>7099</v>
+      </c>
+      <c r="M507" t="s">
         <v>7100</v>
       </c>
-      <c r="B507" t="s">
+      <c r="N507" t="s">
         <v>7101</v>
       </c>
-      <c r="C507" t="s">
+      <c r="O507" t="s">
         <v>7102</v>
-      </c>
-      <c r="D507" t="s">
-        <v>7103</v>
-      </c>
-      <c r="E507" t="s">
-        <v>7104</v>
-      </c>
-      <c r="F507" t="s">
-        <v>7105</v>
-      </c>
-      <c r="G507" t="s">
-        <v>7106</v>
-      </c>
-      <c r="H507" t="s">
-        <v>7107</v>
-      </c>
-      <c r="I507" t="s">
-        <v>7108</v>
-      </c>
-      <c r="J507" t="s">
-        <v>7109</v>
-      </c>
-      <c r="K507" t="s">
-        <v>7110</v>
-      </c>
-      <c r="L507" t="s">
-        <v>7111</v>
-      </c>
-      <c r="M507" t="s">
-        <v>7112</v>
-      </c>
-      <c r="N507" t="s">
-        <v>7113</v>
-      </c>
-      <c r="O507" t="s">
-        <v>7114</v>
       </c>
     </row>
     <row r="508" spans="1:15">
       <c r="A508" t="s">
+        <v>7103</v>
+      </c>
+      <c r="B508" t="s">
+        <v>7104</v>
+      </c>
+      <c r="C508" t="s">
+        <v>7105</v>
+      </c>
+      <c r="D508" t="s">
+        <v>7106</v>
+      </c>
+      <c r="E508" t="s">
+        <v>7107</v>
+      </c>
+      <c r="F508" t="s">
+        <v>7108</v>
+      </c>
+      <c r="G508" t="s">
+        <v>7109</v>
+      </c>
+      <c r="H508" t="s">
+        <v>7110</v>
+      </c>
+      <c r="I508" t="s">
+        <v>7111</v>
+      </c>
+      <c r="J508" t="s">
+        <v>7112</v>
+      </c>
+      <c r="K508" t="s">
+        <v>7113</v>
+      </c>
+      <c r="L508" t="s">
+        <v>7114</v>
+      </c>
+      <c r="M508" t="s">
         <v>7115</v>
       </c>
-      <c r="B508" t="s">
+      <c r="N508" t="s">
         <v>7116</v>
       </c>
-      <c r="C508" t="s">
-        <v>7117</v>
-      </c>
-      <c r="D508" t="s">
-        <v>7118</v>
-      </c>
-      <c r="E508" t="s">
-        <v>7119</v>
-      </c>
-      <c r="F508" t="s">
-        <v>7120</v>
-      </c>
-      <c r="G508" t="s">
-        <v>7121</v>
-      </c>
-      <c r="H508" t="s">
-        <v>7122</v>
-      </c>
-      <c r="I508" t="s">
-        <v>7123</v>
-      </c>
-      <c r="J508" t="s">
-        <v>7124</v>
-      </c>
-      <c r="K508" t="s">
-        <v>7125</v>
-      </c>
-      <c r="L508" t="s">
-        <v>7126</v>
-      </c>
-      <c r="M508" t="s">
-        <v>7127</v>
-      </c>
-      <c r="N508" t="s">
-        <v>7128</v>
-      </c>
       <c r="O508" t="s">
-        <v>7116</v>
+        <v>7104</v>
       </c>
     </row>
     <row r="509" spans="1:15">
       <c r="A509" t="s">
-        <v>7129</v>
+        <v>7117</v>
       </c>
       <c r="B509" t="s">
-        <v>7130</v>
+        <v>7118</v>
       </c>
       <c r="C509" t="s">
-        <v>7131</v>
+        <v>7119</v>
       </c>
       <c r="D509" t="s">
-        <v>7131</v>
+        <v>7119</v>
       </c>
       <c r="E509" t="s">
-        <v>7131</v>
+        <v>7119</v>
       </c>
       <c r="F509" t="s">
-        <v>7131</v>
+        <v>7119</v>
       </c>
       <c r="G509" t="s">
-        <v>7131</v>
+        <v>7119</v>
       </c>
       <c r="H509" t="s">
-        <v>7131</v>
+        <v>7119</v>
       </c>
       <c r="I509" t="s">
-        <v>7131</v>
+        <v>7119</v>
       </c>
       <c r="J509" t="s">
-        <v>7131</v>
+        <v>7119</v>
       </c>
       <c r="K509" t="s">
-        <v>7131</v>
+        <v>7119</v>
       </c>
       <c r="L509" t="s">
-        <v>7131</v>
+        <v>7119</v>
       </c>
       <c r="M509" t="s">
-        <v>7131</v>
+        <v>7119</v>
       </c>
       <c r="N509" t="s">
-        <v>7131</v>
+        <v>7119</v>
       </c>
       <c r="O509" t="s">
-        <v>7130</v>
+        <v>7118</v>
       </c>
     </row>
     <row r="510" spans="1:15">
       <c r="A510" t="s">
-        <v>7132</v>
+        <v>7120</v>
       </c>
       <c r="B510" t="s">
-        <v>7133</v>
+        <v>7121</v>
       </c>
       <c r="C510" t="s">
-        <v>7133</v>
+        <v>7121</v>
       </c>
       <c r="D510" t="s">
-        <v>7133</v>
+        <v>7121</v>
       </c>
       <c r="E510" t="s">
-        <v>7133</v>
+        <v>7121</v>
       </c>
       <c r="F510" t="s">
-        <v>7133</v>
+        <v>7121</v>
       </c>
       <c r="G510" t="s">
-        <v>7133</v>
+        <v>7121</v>
       </c>
       <c r="H510" t="s">
-        <v>7133</v>
+        <v>7121</v>
       </c>
       <c r="I510" t="s">
-        <v>7133</v>
+        <v>7121</v>
       </c>
       <c r="J510" t="s">
-        <v>7133</v>
+        <v>7121</v>
       </c>
       <c r="K510" t="s">
-        <v>7133</v>
+        <v>7121</v>
       </c>
       <c r="L510" t="s">
-        <v>7133</v>
+        <v>7121</v>
       </c>
       <c r="M510" t="s">
-        <v>7133</v>
+        <v>7121</v>
       </c>
       <c r="N510" t="s">
-        <v>7133</v>
+        <v>7121</v>
       </c>
       <c r="O510" t="s">
-        <v>7133</v>
+        <v>7121</v>
       </c>
     </row>
     <row r="511" spans="1:15">
       <c r="A511" t="s">
-        <v>7134</v>
+        <v>7122</v>
       </c>
       <c r="B511" t="s">
-        <v>7135</v>
+        <v>7123</v>
       </c>
       <c r="C511" t="s">
-        <v>7135</v>
+        <v>7123</v>
       </c>
       <c r="D511" t="s">
-        <v>7135</v>
+        <v>7123</v>
       </c>
       <c r="E511" t="s">
-        <v>7135</v>
+        <v>7123</v>
       </c>
       <c r="F511" t="s">
-        <v>7135</v>
+        <v>7123</v>
       </c>
       <c r="G511" t="s">
-        <v>7135</v>
+        <v>7123</v>
       </c>
       <c r="H511" t="s">
-        <v>7135</v>
+        <v>7123</v>
       </c>
       <c r="I511" t="s">
-        <v>7135</v>
+        <v>7123</v>
       </c>
       <c r="J511" t="s">
-        <v>7135</v>
+        <v>7123</v>
       </c>
       <c r="K511" t="s">
-        <v>7135</v>
+        <v>7123</v>
       </c>
       <c r="L511" t="s">
-        <v>7135</v>
+        <v>7123</v>
       </c>
       <c r="M511" t="s">
-        <v>7135</v>
+        <v>7123</v>
       </c>
       <c r="N511" t="s">
-        <v>7135</v>
+        <v>7123</v>
       </c>
       <c r="O511" t="s">
-        <v>7135</v>
+        <v>7123</v>
       </c>
     </row>
     <row r="512" spans="1:15">
       <c r="A512" t="s">
-        <v>7136</v>
+        <v>7124</v>
       </c>
       <c r="B512" t="s">
-        <v>7137</v>
+        <v>7125</v>
       </c>
       <c r="C512" t="s">
-        <v>7137</v>
+        <v>7125</v>
       </c>
       <c r="D512" t="s">
-        <v>7138</v>
+        <v>7126</v>
       </c>
       <c r="E512" t="s">
-        <v>7138</v>
+        <v>7126</v>
       </c>
       <c r="F512" t="s">
-        <v>7138</v>
+        <v>7126</v>
       </c>
       <c r="G512" t="s">
-        <v>7138</v>
+        <v>7126</v>
       </c>
       <c r="H512" t="s">
-        <v>7138</v>
+        <v>7126</v>
       </c>
       <c r="I512" t="s">
-        <v>7138</v>
+        <v>7126</v>
       </c>
       <c r="J512" t="s">
-        <v>7138</v>
+        <v>7126</v>
       </c>
       <c r="K512" t="s">
-        <v>7138</v>
+        <v>7126</v>
       </c>
       <c r="L512" t="s">
-        <v>7138</v>
+        <v>7126</v>
       </c>
       <c r="M512" t="s">
-        <v>7138</v>
+        <v>7126</v>
       </c>
       <c r="N512" t="s">
-        <v>7138</v>
+        <v>7126</v>
       </c>
       <c r="O512" t="s">
-        <v>7138</v>
+        <v>7126</v>
       </c>
     </row>
     <row r="513" spans="1:15">
       <c r="A513" s="1" t="s">
-        <v>7139</v>
+        <v>7127</v>
       </c>
       <c r="B513" s="1" t="s">
-        <v>7140</v>
+        <v>7128</v>
       </c>
       <c r="C513" s="1" t="s">
-        <v>7140</v>
+        <v>7128</v>
       </c>
       <c r="D513" s="1" t="s">
-        <v>7140</v>
+        <v>7128</v>
       </c>
       <c r="E513" s="1" t="s">
-        <v>7140</v>
+        <v>7128</v>
       </c>
       <c r="F513" s="1" t="s">
-        <v>7140</v>
+        <v>7128</v>
       </c>
       <c r="G513" s="1" t="s">
-        <v>7140</v>
+        <v>7128</v>
       </c>
       <c r="H513" s="1" t="s">
-        <v>7140</v>
+        <v>7128</v>
       </c>
       <c r="I513" s="1" t="s">
-        <v>7140</v>
+        <v>7128</v>
       </c>
       <c r="J513" s="1" t="s">
-        <v>7140</v>
+        <v>7128</v>
       </c>
       <c r="K513" s="1" t="s">
-        <v>7140</v>
+        <v>7128</v>
       </c>
       <c r="L513" s="1" t="s">
-        <v>7140</v>
+        <v>7128</v>
       </c>
       <c r="M513" s="1" t="s">
-        <v>7140</v>
+        <v>7128</v>
       </c>
       <c r="N513" s="1" t="s">
-        <v>7140</v>
+        <v>7128</v>
       </c>
       <c r="O513" s="1" t="s">
-        <v>7140</v>
+        <v>7128</v>
       </c>
     </row>
     <row r="514" spans="1:15">
       <c r="A514" s="1" t="s">
-        <v>7141</v>
+        <v>7129</v>
       </c>
       <c r="B514" s="2" t="s">
-        <v>7142</v>
+        <v>7130</v>
       </c>
       <c r="C514" s="2" t="s">
-        <v>7142</v>
+        <v>7130</v>
       </c>
       <c r="D514" s="2" t="s">
-        <v>7142</v>
+        <v>7130</v>
       </c>
       <c r="E514" s="2" t="s">
-        <v>7142</v>
+        <v>7130</v>
       </c>
       <c r="F514" s="2" t="s">
-        <v>7142</v>
+        <v>7130</v>
       </c>
       <c r="G514" s="2" t="s">
-        <v>7142</v>
+        <v>7130</v>
       </c>
       <c r="H514" s="2" t="s">
-        <v>7142</v>
+        <v>7130</v>
       </c>
       <c r="I514" s="2" t="s">
-        <v>7142</v>
+        <v>7130</v>
       </c>
       <c r="J514" s="2" t="s">
-        <v>7142</v>
+        <v>7130</v>
       </c>
       <c r="K514" s="2" t="s">
-        <v>7142</v>
+        <v>7130</v>
       </c>
       <c r="L514" s="2" t="s">
-        <v>7142</v>
+        <v>7130</v>
       </c>
       <c r="M514" s="2" t="s">
-        <v>7142</v>
+        <v>7130</v>
       </c>
       <c r="N514" s="2" t="s">
-        <v>7142</v>
+        <v>7130</v>
       </c>
       <c r="O514" s="2" t="s">
-        <v>7142</v>
+        <v>7130</v>
       </c>
     </row>
     <row r="515" spans="1:15">
       <c r="A515" s="3" t="s">
-        <v>7143</v>
+        <v>7131</v>
       </c>
       <c r="B515" s="1" t="s">
-        <v>7144</v>
+        <v>7132</v>
       </c>
       <c r="C515" s="1" t="s">
-        <v>7144</v>
+        <v>7132</v>
       </c>
       <c r="D515" s="1" t="s">
-        <v>7144</v>
+        <v>7132</v>
       </c>
       <c r="E515" s="1" t="s">
-        <v>7144</v>
+        <v>7132</v>
       </c>
       <c r="F515" s="1" t="s">
-        <v>7144</v>
+        <v>7132</v>
       </c>
       <c r="G515" s="1" t="s">
-        <v>7144</v>
+        <v>7132</v>
       </c>
       <c r="H515" s="1" t="s">
-        <v>7144</v>
+        <v>7132</v>
       </c>
       <c r="I515" s="1" t="s">
-        <v>7144</v>
+        <v>7132</v>
       </c>
       <c r="J515" s="1" t="s">
-        <v>7144</v>
+        <v>7132</v>
       </c>
       <c r="K515" s="1" t="s">
-        <v>7144</v>
+        <v>7132</v>
       </c>
       <c r="L515" s="1" t="s">
-        <v>7144</v>
+        <v>7132</v>
       </c>
       <c r="M515" s="1" t="s">
-        <v>7144</v>
+        <v>7132</v>
       </c>
       <c r="N515" s="1" t="s">
-        <v>7144</v>
+        <v>7132</v>
       </c>
       <c r="O515" s="1" t="s">
-        <v>7144</v>
+        <v>7132</v>
       </c>
     </row>
     <row r="516" spans="1:15">
       <c r="A516" s="1" t="s">
-        <v>7145</v>
+        <v>7133</v>
       </c>
       <c r="B516" s="1" t="s">
-        <v>7146</v>
+        <v>7134</v>
       </c>
       <c r="C516" s="1" t="s">
-        <v>7146</v>
+        <v>7134</v>
       </c>
       <c r="D516" s="1" t="s">
-        <v>7146</v>
+        <v>7134</v>
       </c>
       <c r="E516" s="1" t="s">
-        <v>7146</v>
+        <v>7134</v>
       </c>
       <c r="F516" s="1" t="s">
-        <v>7146</v>
+        <v>7134</v>
       </c>
       <c r="G516" s="1" t="s">
-        <v>7146</v>
+        <v>7134</v>
       </c>
       <c r="H516" s="1" t="s">
-        <v>7146</v>
+        <v>7134</v>
       </c>
       <c r="I516" s="1" t="s">
-        <v>7146</v>
+        <v>7134</v>
       </c>
       <c r="J516" s="1" t="s">
-        <v>7146</v>
+        <v>7134</v>
       </c>
       <c r="K516" s="1" t="s">
-        <v>7146</v>
+        <v>7134</v>
       </c>
       <c r="L516" s="1" t="s">
-        <v>7146</v>
+        <v>7134</v>
       </c>
       <c r="M516" s="1" t="s">
-        <v>7146</v>
+        <v>7134</v>
       </c>
       <c r="N516" s="1" t="s">
-        <v>7146</v>
+        <v>7134</v>
       </c>
       <c r="O516" s="1" t="s">
-        <v>7146</v>
+        <v>7134</v>
       </c>
     </row>
     <row r="517" spans="1:15">
       <c r="A517" s="1" t="s">
-        <v>7147</v>
+        <v>7135</v>
       </c>
       <c r="B517" s="1" t="s">
-        <v>7148</v>
+        <v>7136</v>
       </c>
       <c r="C517" s="1" t="s">
-        <v>7148</v>
+        <v>7136</v>
       </c>
       <c r="D517" s="1" t="s">
-        <v>7148</v>
+        <v>7136</v>
       </c>
       <c r="E517" s="1" t="s">
-        <v>7148</v>
+        <v>7136</v>
       </c>
       <c r="F517" s="1" t="s">
-        <v>7148</v>
+        <v>7136</v>
       </c>
       <c r="G517" s="1" t="s">
-        <v>7148</v>
+        <v>7136</v>
       </c>
       <c r="H517" s="1" t="s">
-        <v>7148</v>
+        <v>7136</v>
       </c>
       <c r="I517" s="1" t="s">
-        <v>7148</v>
+        <v>7136</v>
       </c>
       <c r="J517" s="1" t="s">
-        <v>7148</v>
+        <v>7136</v>
       </c>
       <c r="K517" s="1" t="s">
-        <v>7148</v>
+        <v>7136</v>
       </c>
       <c r="L517" s="1" t="s">
-        <v>7148</v>
+        <v>7136</v>
       </c>
       <c r="M517" s="1" t="s">
-        <v>7148</v>
+        <v>7136</v>
       </c>
       <c r="N517" s="1" t="s">
-        <v>7148</v>
+        <v>7136</v>
       </c>
       <c r="O517" s="1" t="s">
-        <v>7148</v>
+        <v>7136</v>
       </c>
     </row>
     <row r="518" spans="1:15">
       <c r="A518" s="1" t="s">
-        <v>7149</v>
+        <v>7137</v>
       </c>
       <c r="B518" s="1" t="s">
-        <v>7150</v>
+        <v>7138</v>
       </c>
       <c r="C518" s="1" t="s">
-        <v>7150</v>
+        <v>7138</v>
       </c>
       <c r="D518" s="1" t="s">
-        <v>7150</v>
+        <v>7138</v>
       </c>
       <c r="E518" s="1" t="s">
-        <v>7150</v>
+        <v>7138</v>
       </c>
       <c r="F518" s="1" t="s">
-        <v>7150</v>
+        <v>7138</v>
       </c>
       <c r="G518" s="1" t="s">
-        <v>7150</v>
+        <v>7138</v>
       </c>
       <c r="H518" s="1" t="s">
-        <v>7150</v>
+        <v>7138</v>
       </c>
       <c r="I518" s="1" t="s">
-        <v>7150</v>
+        <v>7138</v>
       </c>
       <c r="J518" s="1" t="s">
-        <v>7150</v>
+        <v>7138</v>
       </c>
       <c r="K518" s="1" t="s">
-        <v>7150</v>
+        <v>7138</v>
       </c>
       <c r="L518" s="1" t="s">
-        <v>7150</v>
+        <v>7138</v>
       </c>
       <c r="M518" s="1" t="s">
-        <v>7150</v>
+        <v>7138</v>
       </c>
       <c r="N518" s="1" t="s">
-        <v>7150</v>
+        <v>7138</v>
       </c>
       <c r="O518" s="1" t="s">
-        <v>7150</v>
+        <v>7138</v>
       </c>
     </row>
     <row r="519" spans="1:15">
       <c r="A519" s="1" t="s">
-        <v>7151</v>
+        <v>7139</v>
       </c>
       <c r="B519" s="1" t="s">
-        <v>7152</v>
+        <v>7140</v>
       </c>
       <c r="C519" s="1" t="s">
-        <v>7152</v>
+        <v>7140</v>
       </c>
       <c r="D519" s="1" t="s">
-        <v>7152</v>
+        <v>7140</v>
       </c>
       <c r="E519" s="1" t="s">
-        <v>7152</v>
+        <v>7140</v>
       </c>
       <c r="F519" s="1" t="s">
-        <v>7152</v>
+        <v>7140</v>
       </c>
       <c r="G519" s="1" t="s">
-        <v>7152</v>
+        <v>7140</v>
       </c>
       <c r="H519" s="1" t="s">
-        <v>7152</v>
+        <v>7140</v>
       </c>
       <c r="I519" s="1" t="s">
-        <v>7152</v>
+        <v>7140</v>
       </c>
       <c r="J519" s="1" t="s">
-        <v>7152</v>
+        <v>7140</v>
       </c>
       <c r="K519" s="1" t="s">
-        <v>7152</v>
+        <v>7140</v>
       </c>
       <c r="L519" s="1" t="s">
-        <v>7152</v>
+        <v>7140</v>
       </c>
       <c r="M519" s="1" t="s">
-        <v>7152</v>
+        <v>7140</v>
       </c>
       <c r="N519" s="1" t="s">
-        <v>7152</v>
+        <v>7140</v>
       </c>
       <c r="O519" s="1" t="s">
-        <v>7152</v>
+        <v>7140</v>
       </c>
     </row>
     <row r="520" spans="1:15">
       <c r="A520" s="1" t="s">
-        <v>7153</v>
+        <v>7141</v>
       </c>
       <c r="B520" s="1" t="s">
-        <v>7154</v>
+        <v>7142</v>
       </c>
       <c r="C520" s="1" t="s">
-        <v>7154</v>
+        <v>7142</v>
       </c>
       <c r="D520" s="1" t="s">
-        <v>7154</v>
+        <v>7142</v>
       </c>
       <c r="E520" s="1" t="s">
-        <v>7154</v>
+        <v>7142</v>
       </c>
       <c r="F520" s="1" t="s">
-        <v>7154</v>
+        <v>7142</v>
       </c>
       <c r="G520" s="1" t="s">
-        <v>7154</v>
+        <v>7142</v>
       </c>
       <c r="H520" s="1" t="s">
-        <v>7154</v>
+        <v>7142</v>
       </c>
       <c r="I520" s="1" t="s">
-        <v>7154</v>
+        <v>7142</v>
       </c>
       <c r="J520" s="1" t="s">
-        <v>7154</v>
+        <v>7142</v>
       </c>
       <c r="K520" s="1" t="s">
-        <v>7154</v>
+        <v>7142</v>
       </c>
       <c r="L520" s="1" t="s">
-        <v>7154</v>
+        <v>7142</v>
       </c>
       <c r="M520" s="1" t="s">
-        <v>7154</v>
+        <v>7142</v>
       </c>
       <c r="N520" s="1" t="s">
-        <v>7154</v>
+        <v>7142</v>
       </c>
       <c r="O520" s="1" t="s">
-        <v>7154</v>
+        <v>7142</v>
       </c>
     </row>
     <row r="521" spans="1:15">
       <c r="A521" s="1" t="s">
-        <v>7155</v>
+        <v>7143</v>
       </c>
       <c r="B521" s="1" t="s">
-        <v>7156</v>
+        <v>7144</v>
       </c>
       <c r="C521" s="1" t="s">
-        <v>7156</v>
+        <v>7144</v>
       </c>
       <c r="D521" s="1" t="s">
-        <v>7156</v>
+        <v>7144</v>
       </c>
       <c r="E521" s="1" t="s">
-        <v>7156</v>
+        <v>7144</v>
       </c>
       <c r="F521" s="1" t="s">
-        <v>7156</v>
+        <v>7144</v>
       </c>
       <c r="G521" s="1" t="s">
-        <v>7156</v>
+        <v>7144</v>
       </c>
       <c r="H521" s="1" t="s">
-        <v>7156</v>
+        <v>7144</v>
       </c>
       <c r="I521" s="1" t="s">
-        <v>7156</v>
+        <v>7144</v>
       </c>
       <c r="J521" s="1" t="s">
-        <v>7156</v>
+        <v>7144</v>
       </c>
       <c r="K521" s="1" t="s">
-        <v>7156</v>
+        <v>7144</v>
       </c>
       <c r="L521" s="1" t="s">
-        <v>7156</v>
+        <v>7144</v>
       </c>
       <c r="M521" s="1" t="s">
-        <v>7156</v>
+        <v>7144</v>
       </c>
       <c r="N521" s="1" t="s">
-        <v>7156</v>
+        <v>7144</v>
       </c>
       <c r="O521" s="1" t="s">
-        <v>7156</v>
+        <v>7144</v>
       </c>
     </row>
     <row r="522" spans="1:15">
       <c r="A522" s="4" t="s">
-        <v>7157</v>
+        <v>7145</v>
       </c>
       <c r="B522" s="1" t="s">
-        <v>7158</v>
+        <v>7146</v>
       </c>
       <c r="C522" s="1" t="s">
-        <v>7158</v>
+        <v>7146</v>
       </c>
       <c r="D522" s="1" t="s">
-        <v>7158</v>
+        <v>7146</v>
       </c>
       <c r="E522" s="1" t="s">
-        <v>7158</v>
+        <v>7146</v>
       </c>
       <c r="F522" s="1" t="s">
-        <v>7158</v>
+        <v>7146</v>
       </c>
       <c r="G522" s="1" t="s">
-        <v>7158</v>
+        <v>7146</v>
       </c>
       <c r="H522" s="1" t="s">
-        <v>7158</v>
+        <v>7146</v>
       </c>
       <c r="I522" s="1" t="s">
-        <v>7158</v>
+        <v>7146</v>
       </c>
       <c r="J522" s="1" t="s">
-        <v>7158</v>
+        <v>7146</v>
       </c>
       <c r="K522" s="1" t="s">
-        <v>7158</v>
+        <v>7146</v>
       </c>
       <c r="L522" s="1" t="s">
-        <v>7158</v>
+        <v>7146</v>
       </c>
       <c r="M522" s="1" t="s">
-        <v>7158</v>
+        <v>7146</v>
       </c>
       <c r="N522" s="1" t="s">
-        <v>7158</v>
+        <v>7146</v>
       </c>
       <c r="O522" s="1" t="s">
-        <v>7158</v>
+        <v>7146</v>
       </c>
     </row>
     <row r="523" spans="1:15">
       <c r="A523" s="1" t="s">
-        <v>7159</v>
+        <v>7147</v>
       </c>
       <c r="B523" s="1" t="s">
-        <v>7160</v>
+        <v>7148</v>
       </c>
       <c r="C523" s="1" t="s">
-        <v>7160</v>
+        <v>7148</v>
       </c>
       <c r="D523" s="1" t="s">
-        <v>7160</v>
+        <v>7148</v>
       </c>
       <c r="E523" s="1" t="s">
-        <v>7160</v>
+        <v>7148</v>
       </c>
       <c r="F523" s="1" t="s">
-        <v>7160</v>
+        <v>7148</v>
       </c>
       <c r="G523" s="1" t="s">
-        <v>7160</v>
+        <v>7148</v>
       </c>
       <c r="H523" s="1" t="s">
-        <v>7160</v>
+        <v>7148</v>
       </c>
       <c r="I523" s="1" t="s">
-        <v>7160</v>
+        <v>7148</v>
       </c>
       <c r="J523" s="1" t="s">
-        <v>7160</v>
+        <v>7148</v>
       </c>
       <c r="K523" s="1" t="s">
-        <v>7160</v>
+        <v>7148</v>
       </c>
       <c r="L523" s="1" t="s">
-        <v>7160</v>
+        <v>7148</v>
       </c>
       <c r="M523" s="1" t="s">
-        <v>7160</v>
+        <v>7148</v>
       </c>
       <c r="N523" s="1" t="s">
-        <v>7160</v>
+        <v>7148</v>
       </c>
       <c r="O523" s="1" t="s">
-        <v>7160</v>
+        <v>7148</v>
       </c>
     </row>
     <row r="524" spans="1:15">
       <c r="A524" s="1" t="s">
-        <v>7161</v>
+        <v>7149</v>
       </c>
       <c r="B524" s="1" t="s">
-        <v>7162</v>
+        <v>7150</v>
       </c>
       <c r="C524" s="1" t="s">
-        <v>7162</v>
+        <v>7150</v>
       </c>
       <c r="D524" s="1" t="s">
-        <v>7162</v>
+        <v>7150</v>
       </c>
       <c r="E524" s="1" t="s">
-        <v>7162</v>
+        <v>7150</v>
       </c>
       <c r="F524" s="1" t="s">
-        <v>7162</v>
+        <v>7150</v>
       </c>
       <c r="G524" s="1" t="s">
-        <v>7162</v>
+        <v>7150</v>
       </c>
       <c r="H524" s="1" t="s">
-        <v>7162</v>
+        <v>7150</v>
       </c>
       <c r="I524" s="1" t="s">
-        <v>7162</v>
+        <v>7150</v>
       </c>
       <c r="J524" s="1" t="s">
-        <v>7162</v>
+        <v>7150</v>
       </c>
       <c r="K524" s="1" t="s">
-        <v>7162</v>
+        <v>7150</v>
       </c>
       <c r="L524" s="1" t="s">
-        <v>7162</v>
+        <v>7150</v>
       </c>
       <c r="M524" s="1" t="s">
-        <v>7162</v>
+        <v>7150</v>
       </c>
       <c r="N524" s="1" t="s">
-        <v>7162</v>
+        <v>7150</v>
       </c>
       <c r="O524" s="1" t="s">
-        <v>7162</v>
+        <v>7150</v>
       </c>
     </row>
     <row r="525" spans="1:15">
       <c r="A525" s="1" t="s">
-        <v>7163</v>
+        <v>7151</v>
       </c>
       <c r="B525" s="1" t="s">
-        <v>7164</v>
+        <v>7152</v>
       </c>
       <c r="C525" s="1" t="s">
-        <v>7164</v>
+        <v>7152</v>
       </c>
       <c r="D525" s="1" t="s">
-        <v>7164</v>
+        <v>7152</v>
       </c>
       <c r="E525" s="1" t="s">
-        <v>7164</v>
+        <v>7152</v>
       </c>
       <c r="F525" s="1" t="s">
-        <v>7164</v>
+        <v>7152</v>
       </c>
       <c r="G525" s="1" t="s">
-        <v>7164</v>
+        <v>7152</v>
       </c>
       <c r="H525" s="1" t="s">
-        <v>7164</v>
+        <v>7152</v>
       </c>
       <c r="I525" s="1" t="s">
-        <v>7164</v>
+        <v>7152</v>
       </c>
       <c r="J525" s="1" t="s">
-        <v>7164</v>
+        <v>7152</v>
       </c>
       <c r="K525" s="1" t="s">
-        <v>7164</v>
+        <v>7152</v>
       </c>
       <c r="L525" s="1" t="s">
-        <v>7164</v>
+        <v>7152</v>
       </c>
       <c r="M525" s="1" t="s">
-        <v>7164</v>
+        <v>7152</v>
       </c>
       <c r="N525" s="1" t="s">
-        <v>7164</v>
+        <v>7152</v>
       </c>
       <c r="O525" s="1" t="s">
-        <v>7164</v>
+        <v>7152</v>
       </c>
     </row>
     <row r="526" spans="1:15">
       <c r="A526" s="1" t="s">
-        <v>7165</v>
+        <v>7153</v>
       </c>
       <c r="B526" s="1" t="s">
-        <v>7166</v>
+        <v>7154</v>
       </c>
       <c r="C526" s="1" t="s">
-        <v>7167</v>
+        <v>7155</v>
       </c>
       <c r="D526" s="1" t="s">
-        <v>7167</v>
+        <v>7155</v>
       </c>
       <c r="E526" s="1" t="s">
-        <v>7167</v>
+        <v>7155</v>
       </c>
       <c r="F526" s="1" t="s">
-        <v>7167</v>
+        <v>7155</v>
       </c>
       <c r="G526" s="1" t="s">
-        <v>7167</v>
+        <v>7155</v>
       </c>
       <c r="H526" s="1" t="s">
-        <v>7167</v>
+        <v>7155</v>
       </c>
       <c r="I526" s="1" t="s">
-        <v>7167</v>
+        <v>7155</v>
       </c>
       <c r="J526" s="1" t="s">
-        <v>7167</v>
+        <v>7155</v>
       </c>
       <c r="K526" s="1" t="s">
-        <v>7167</v>
+        <v>7155</v>
       </c>
       <c r="L526" s="1" t="s">
-        <v>7167</v>
+        <v>7155</v>
       </c>
       <c r="M526" s="1" t="s">
-        <v>7167</v>
+        <v>7155</v>
       </c>
       <c r="N526" s="1" t="s">
-        <v>7167</v>
+        <v>7155</v>
       </c>
       <c r="O526" s="1" t="s">
-        <v>7167</v>
+        <v>7155</v>
       </c>
     </row>
   </sheetData>
@@ -47298,7 +47262,7 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A249 A119:O248 A118 A1:O117 C275 A275 A250:O274 A498 A499:O500 A501 A502:O508 C118:O118 A449:O497 C448:O448 A448 A277:O447" numberStoredAsText="1"/>
+    <ignoredError sqref="A277:O447 A448 C448:O448 A449:O467 A469:O497 C118:O118 A502:O508 A501 A499:O500 A498 A250:O274 A275 C275 A1:O117 A118 A119:O248 A249" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>